--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -60,7 +60,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Q4"/>
+  <dimension ref="A1:R4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -149,6 +149,11 @@
           <t>years to transition ats</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>profit margin</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -167,40 +172,43 @@
         <v>0.7</v>
       </c>
       <c r="F2" t="n">
-        <v>7.0</v>
+        <v>9.59217253160857</v>
       </c>
       <c r="G2" t="n">
-        <v>3.6687854661123813</v>
+        <v>8.393616962771578</v>
       </c>
       <c r="H2" t="n">
-        <v>3.036354611073011</v>
+        <v>5.995702918702903</v>
       </c>
       <c r="I2" t="n">
-        <v>50.0</v>
+        <v>159.17100275103942</v>
       </c>
       <c r="J2" t="n">
-        <v>50.0</v>
+        <v>144.42540564720525</v>
       </c>
       <c r="K2" t="n">
-        <v>50.0</v>
+        <v>108.44527521712024</v>
       </c>
       <c r="L2" t="n">
         <v>0.0</v>
       </c>
       <c r="M2" t="n">
-        <v>0.074378311174592</v>
+        <v>0.09400847705046052</v>
       </c>
       <c r="N2" t="n">
-        <v>0.7836673784769767</v>
+        <v>0.7837580175461181</v>
       </c>
       <c r="O2" t="n">
-        <v>0.7107624561038625</v>
+        <v>0.7111506974068387</v>
       </c>
       <c r="P2" t="n">
         <v>0.5339845351691</v>
       </c>
       <c r="Q2" t="n">
         <v>25.0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="3">
@@ -220,40 +228,43 @@
         <v>0.7</v>
       </c>
       <c r="F3" t="n">
-        <v>9.485901677703112</v>
+        <v>10.246015625138003</v>
       </c>
       <c r="G3" t="n">
-        <v>8.897348088767941</v>
+        <v>8.654383431501124</v>
       </c>
       <c r="H3" t="n">
-        <v>7.0</v>
+        <v>5.995702918702903</v>
       </c>
       <c r="I3" t="n">
-        <v>150.0</v>
+        <v>174.34313093409196</v>
       </c>
       <c r="J3" t="n">
-        <v>150.0</v>
+        <v>146.1507987542513</v>
       </c>
       <c r="K3" t="n">
-        <v>150.0</v>
+        <v>108.44527521712024</v>
       </c>
       <c r="L3" t="n">
         <v>0.0</v>
       </c>
       <c r="M3" t="n">
-        <v>0.39062288206894125</v>
+        <v>0.38049498236678936</v>
       </c>
       <c r="N3" t="n">
-        <v>0.8608968250980082</v>
+        <v>0.8584655767194689</v>
       </c>
       <c r="O3" t="n">
-        <v>0.720173909128709</v>
+        <v>0.7196465330659335</v>
       </c>
       <c r="P3" t="n">
         <v>0.5339845351691</v>
       </c>
       <c r="Q3" t="n">
         <v>25.0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.2</v>
       </c>
     </row>
     <row r="4">
@@ -273,40 +284,43 @@
         <v>0.7</v>
       </c>
       <c r="F4" t="n">
-        <v>7.0</v>
+        <v>9.908336098022382</v>
       </c>
       <c r="G4" t="n">
-        <v>6.310206048183373</v>
+        <v>8.531879085280357</v>
       </c>
       <c r="H4" t="n">
-        <v>5.592853230563756</v>
+        <v>5.995702918702903</v>
       </c>
       <c r="I4" t="n">
-        <v>100.0</v>
+        <v>165.42721203353108</v>
       </c>
       <c r="J4" t="n">
-        <v>100.0</v>
+        <v>145.18328430147182</v>
       </c>
       <c r="K4" t="n">
-        <v>100.0</v>
+        <v>108.44527521712024</v>
       </c>
       <c r="L4" t="n">
         <v>0.0</v>
       </c>
       <c r="M4" t="n">
-        <v>0.20570672405411677</v>
+        <v>0.1976116120986026</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8165068604892819</v>
+        <v>0.814563592053107</v>
       </c>
       <c r="O4" t="n">
-        <v>0.7153885453847253</v>
+        <v>0.714882491900447</v>
       </c>
       <c r="P4" t="n">
         <v>0.5339845351691</v>
       </c>
       <c r="Q4" t="n">
         <v>25.0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.15</v>
       </c>
     </row>
   </sheetData>

--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -60,7 +60,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:U17"/>
+  <dimension ref="A1:U16"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -181,49 +181,49 @@
         <v>0.1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="E2" t="n">
         <v>0.7</v>
       </c>
       <c r="F2" t="n">
-        <v>36.28940687876643</v>
+        <v>28.41097645332293</v>
       </c>
       <c r="G2" t="n">
-        <v>19.716959407525085</v>
+        <v>16.50237684348026</v>
       </c>
       <c r="H2" t="n">
-        <v>12.541144704611776</v>
+        <v>10.545823234677838</v>
       </c>
       <c r="I2" t="n">
-        <v>234.28749518938986</v>
+        <v>195.2795744295943</v>
       </c>
       <c r="J2" t="n">
-        <v>189.39065061880427</v>
+        <v>147.5371247524124</v>
       </c>
       <c r="K2" t="n">
-        <v>111.67769253169617</v>
+        <v>105.94417321878504</v>
       </c>
       <c r="L2" t="n">
         <v>0.0</v>
       </c>
       <c r="M2" t="n">
-        <v>0.9978058397019188</v>
+        <v>0.9486999753389981</v>
       </c>
       <c r="N2" t="n">
-        <v>1.1536316263125557</v>
+        <v>0.9615566244913223</v>
       </c>
       <c r="O2" t="n">
-        <v>0.9325595636469917</v>
+        <v>0.7264728022808785</v>
       </c>
       <c r="P2" t="n">
-        <v>0.549900958026072</v>
+        <v>0.5216691089292975</v>
       </c>
       <c r="Q2" t="n">
-        <v>25.0</v>
+        <v>35.0</v>
       </c>
       <c r="R2" t="n">
-        <v>4950000.0</v>
+        <v>900000.0</v>
       </c>
       <c r="S2" t="n">
         <v>0.08</v>
@@ -246,49 +246,49 @@
         <v>0.1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="E3" t="n">
         <v>0.7</v>
       </c>
       <c r="F3" t="n">
-        <v>36.3020449623616</v>
+        <v>29.780783977693822</v>
       </c>
       <c r="G3" t="n">
-        <v>19.71718696925032</v>
+        <v>15.58365163678584</v>
       </c>
       <c r="H3" t="n">
-        <v>12.54087422740917</v>
+        <v>10.496061526398798</v>
       </c>
       <c r="I3" t="n">
-        <v>234.28892298163802</v>
+        <v>195.28693645821852</v>
       </c>
       <c r="J3" t="n">
-        <v>189.39404328589242</v>
+        <v>148.27430970996303</v>
       </c>
       <c r="K3" t="n">
-        <v>111.67769253169617</v>
+        <v>105.96533559259294</v>
       </c>
       <c r="L3" t="n">
         <v>0.0</v>
       </c>
       <c r="M3" t="n">
-        <v>0.9978350318503323</v>
+        <v>0.9488662965098728</v>
       </c>
       <c r="N3" t="n">
-        <v>1.1536386567615855</v>
+        <v>0.9615928751202679</v>
       </c>
       <c r="O3" t="n">
-        <v>0.9325762691397338</v>
+        <v>0.730102701011858</v>
       </c>
       <c r="P3" t="n">
-        <v>0.549900958026072</v>
+        <v>0.5217733124579276</v>
       </c>
       <c r="Q3" t="n">
-        <v>25.0</v>
+        <v>35.0</v>
       </c>
       <c r="R3" t="n">
-        <v>5850000.0</v>
+        <v>900000.0</v>
       </c>
       <c r="S3" t="n">
         <v>0.08</v>
@@ -311,49 +311,49 @@
         <v>0.1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="E4" t="n">
         <v>0.7</v>
       </c>
       <c r="F4" t="n">
-        <v>36.31465847197772</v>
+        <v>29.969710495299793</v>
       </c>
       <c r="G4" t="n">
-        <v>19.717425829949526</v>
+        <v>16.964644979867217</v>
       </c>
       <c r="H4" t="n">
-        <v>12.540601633338504</v>
+        <v>10.60809208186763</v>
       </c>
       <c r="I4" t="n">
-        <v>234.29036139475036</v>
+        <v>195.2790628606574</v>
       </c>
       <c r="J4" t="n">
-        <v>189.39744306854502</v>
+        <v>146.95659545461845</v>
       </c>
       <c r="K4" t="n">
-        <v>111.67769253169617</v>
+        <v>105.81719897593761</v>
       </c>
       <c r="L4" t="n">
         <v>0.0</v>
       </c>
       <c r="M4" t="n">
-        <v>0.9978644411492771</v>
+        <v>0.9486884180972501</v>
       </c>
       <c r="N4" t="n">
-        <v>1.1536457395077508</v>
+        <v>0.9615541055258771</v>
       </c>
       <c r="O4" t="n">
-        <v>0.9325930096695163</v>
+        <v>0.7236142760185416</v>
       </c>
       <c r="P4" t="n">
-        <v>0.549900958026072</v>
+        <v>0.5210438877575169</v>
       </c>
       <c r="Q4" t="n">
-        <v>25.0</v>
+        <v>35.0</v>
       </c>
       <c r="R4" t="n">
-        <v>6750000.0</v>
+        <v>900000.0</v>
       </c>
       <c r="S4" t="n">
         <v>0.08</v>
@@ -376,49 +376,49 @@
         <v>0.1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="E5" t="n">
         <v>0.7</v>
       </c>
       <c r="F5" t="n">
-        <v>36.225843068145316</v>
+        <v>30.21357635776602</v>
       </c>
       <c r="G5" t="n">
-        <v>19.715383031408205</v>
+        <v>16.694586352223947</v>
       </c>
       <c r="H5" t="n">
-        <v>12.542484764540083</v>
+        <v>10.553937002892145</v>
       </c>
       <c r="I5" t="n">
-        <v>234.28051554111343</v>
+        <v>195.28145804737852</v>
       </c>
       <c r="J5" t="n">
-        <v>189.37547610345476</v>
+        <v>147.3502025453923</v>
       </c>
       <c r="K5" t="n">
-        <v>111.67769253169617</v>
+        <v>105.90184847116923</v>
       </c>
       <c r="L5" t="n">
         <v>0.0</v>
       </c>
       <c r="M5" t="n">
-        <v>0.9976631362178284</v>
+        <v>0.9487425295766067</v>
       </c>
       <c r="N5" t="n">
-        <v>1.1535972585244425</v>
+        <v>0.9615658994252918</v>
       </c>
       <c r="O5" t="n">
-        <v>0.9324848443334113</v>
+        <v>0.7255523973335115</v>
       </c>
       <c r="P5" t="n">
-        <v>0.549900958026072</v>
+        <v>0.5214607018720373</v>
       </c>
       <c r="Q5" t="n">
-        <v>25.0</v>
+        <v>35.0</v>
       </c>
       <c r="R5" t="n">
-        <v>450000.0</v>
+        <v>900000.0</v>
       </c>
       <c r="S5" t="n">
         <v>0.08</v>
@@ -441,49 +441,49 @@
         <v>0.1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="E6" t="n">
         <v>0.7</v>
       </c>
       <c r="F6" t="n">
-        <v>36.276744085542035</v>
+        <v>29.473923819084238</v>
       </c>
       <c r="G6" t="n">
-        <v>19.716743268394055</v>
+        <v>16.63690746801699</v>
       </c>
       <c r="H6" t="n">
-        <v>12.541413064590323</v>
+        <v>10.552466485108072</v>
       </c>
       <c r="I6" t="n">
-        <v>234.28607801800604</v>
+        <v>195.27244450605397</v>
       </c>
       <c r="J6" t="n">
-        <v>189.38726506728088</v>
+        <v>147.44248471645096</v>
       </c>
       <c r="K6" t="n">
-        <v>111.67769253169617</v>
+        <v>105.92301084497716</v>
       </c>
       <c r="L6" t="n">
         <v>0.0</v>
       </c>
       <c r="M6" t="n">
-        <v>0.9977768647040371</v>
+        <v>0.9485388978300666</v>
       </c>
       <c r="N6" t="n">
-        <v>1.1536246481606618</v>
+        <v>0.9615215167478097</v>
       </c>
       <c r="O6" t="n">
-        <v>0.9325428931912905</v>
+        <v>0.7260067947438049</v>
       </c>
       <c r="P6" t="n">
-        <v>0.549900958026072</v>
+        <v>0.5215649054006675</v>
       </c>
       <c r="Q6" t="n">
-        <v>25.0</v>
+        <v>35.0</v>
       </c>
       <c r="R6" t="n">
-        <v>4050000.0</v>
+        <v>900000.0</v>
       </c>
       <c r="S6" t="n">
         <v>0.08</v>
@@ -506,49 +506,49 @@
         <v>0.1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="E7" t="n">
         <v>0.7</v>
       </c>
       <c r="F7" t="n">
-        <v>36.26405644603796</v>
+        <v>30.186549959802534</v>
       </c>
       <c r="G7" t="n">
-        <v>19.716538677065525</v>
+        <v>16.72682945211705</v>
       </c>
       <c r="H7" t="n">
-        <v>12.541679306991535</v>
+        <v>10.568203666168559</v>
       </c>
       <c r="I7" t="n">
-        <v>234.28467146748648</v>
+        <v>195.27467677153132</v>
       </c>
       <c r="J7" t="n">
-        <v>189.38388663132193</v>
+        <v>147.25758584736147</v>
       </c>
       <c r="K7" t="n">
-        <v>111.67769253169617</v>
+        <v>105.88068609736135</v>
       </c>
       <c r="L7" t="n">
         <v>0.0</v>
       </c>
       <c r="M7" t="n">
-        <v>0.9977481068566875</v>
+        <v>0.9485893286320701</v>
       </c>
       <c r="N7" t="n">
-        <v>1.1536177223059034</v>
+        <v>0.9615325084230202</v>
       </c>
       <c r="O7" t="n">
-        <v>0.9325262577726294</v>
+        <v>0.7250963527124079</v>
       </c>
       <c r="P7" t="n">
-        <v>0.549900958026072</v>
+        <v>0.5213564983434072</v>
       </c>
       <c r="Q7" t="n">
-        <v>25.0</v>
+        <v>35.0</v>
       </c>
       <c r="R7" t="n">
-        <v>3150000.0</v>
+        <v>900000.0</v>
       </c>
       <c r="S7" t="n">
         <v>0.08</v>
@@ -571,49 +571,49 @@
         <v>0.1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="E8" t="n">
         <v>0.7</v>
       </c>
       <c r="F8" t="n">
-        <v>36.25134382259434</v>
+        <v>30.15983371065964</v>
       </c>
       <c r="G8" t="n">
-        <v>19.715733421478888</v>
+        <v>16.796471807428038</v>
       </c>
       <c r="H8" t="n">
-        <v>12.541962868810614</v>
+        <v>10.597017881571995</v>
       </c>
       <c r="I8" t="n">
-        <v>234.28327553783114</v>
+        <v>195.28403909715703</v>
       </c>
       <c r="J8" t="n">
-        <v>189.38219739754905</v>
+        <v>147.16222209971895</v>
       </c>
       <c r="K8" t="n">
-        <v>111.67769253169617</v>
+        <v>105.85952372355341</v>
       </c>
       <c r="L8" t="n">
         <v>0.0</v>
       </c>
       <c r="M8" t="n">
-        <v>0.9977195661598692</v>
+        <v>0.9488008400292219</v>
       </c>
       <c r="N8" t="n">
-        <v>1.1536108487482806</v>
+        <v>0.9615786085144012</v>
       </c>
       <c r="O8" t="n">
-        <v>0.9325179399855309</v>
+        <v>0.7246267816190165</v>
       </c>
       <c r="P8" t="n">
-        <v>0.549900958026072</v>
+        <v>0.521252294814777</v>
       </c>
       <c r="Q8" t="n">
-        <v>25.0</v>
+        <v>35.0</v>
       </c>
       <c r="R8" t="n">
-        <v>2250000.0</v>
+        <v>900000.0</v>
       </c>
       <c r="S8" t="n">
         <v>0.08</v>
@@ -636,49 +636,49 @@
         <v>0.1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="E9" t="n">
         <v>0.7</v>
       </c>
       <c r="F9" t="n">
-        <v>36.23860607653245</v>
+        <v>28.56673852253458</v>
       </c>
       <c r="G9" t="n">
-        <v>19.715552259654807</v>
+        <v>15.478079803252363</v>
       </c>
       <c r="H9" t="n">
-        <v>12.54222487598942</v>
+        <v>10.496878473593608</v>
       </c>
       <c r="I9" t="n">
-        <v>234.2818902290402</v>
+        <v>195.28585880641012</v>
       </c>
       <c r="J9" t="n">
-        <v>189.37883319271955</v>
+        <v>148.32820990917693</v>
       </c>
       <c r="K9" t="n">
-        <v>111.67769253169617</v>
+        <v>106.00766034020876</v>
       </c>
       <c r="L9" t="n">
         <v>0.0</v>
       </c>
       <c r="M9" t="n">
-        <v>0.9976912426135828</v>
+        <v>0.9488419504607455</v>
       </c>
       <c r="N9" t="n">
-        <v>1.153604027487794</v>
+        <v>0.9615875687627634</v>
       </c>
       <c r="O9" t="n">
-        <v>0.9325013746409511</v>
+        <v>0.7303681055927874</v>
       </c>
       <c r="P9" t="n">
-        <v>0.549900958026072</v>
+        <v>0.521981719515188</v>
       </c>
       <c r="Q9" t="n">
-        <v>25.0</v>
+        <v>35.0</v>
       </c>
       <c r="R9" t="n">
-        <v>1350000.0</v>
+        <v>900000.0</v>
       </c>
       <c r="S9" t="n">
         <v>0.08</v>
@@ -701,49 +701,49 @@
         <v>0.1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="E10" t="n">
         <v>0.7</v>
       </c>
       <c r="F10" t="n">
-        <v>36.339812306927044</v>
+        <v>29.867460380569</v>
       </c>
       <c r="G10" t="n">
-        <v>19.71932361272845</v>
+        <v>16.880881194352394</v>
       </c>
       <c r="H10" t="n">
-        <v>12.543240682792895</v>
+        <v>10.605308784976822</v>
       </c>
       <c r="I10" t="n">
-        <v>234.27730091170406</v>
+        <v>195.27341471283276</v>
       </c>
       <c r="J10" t="n">
-        <v>189.39894092325687</v>
+        <v>147.04566799527734</v>
       </c>
       <c r="K10" t="n">
-        <v>111.67769253169617</v>
+        <v>105.83836134974551</v>
       </c>
       <c r="L10" t="n">
         <v>0.0</v>
       </c>
       <c r="M10" t="n">
-        <v>0.997597411012404</v>
+        <v>0.9485608165070605</v>
       </c>
       <c r="N10" t="n">
-        <v>1.1535814296892308</v>
+        <v>0.9615262940459884</v>
       </c>
       <c r="O10" t="n">
-        <v>0.9326003851061165</v>
+        <v>0.7240528692087459</v>
       </c>
       <c r="P10" t="n">
-        <v>0.549900958026072</v>
+        <v>0.5211480912861469</v>
       </c>
       <c r="Q10" t="n">
-        <v>25.0</v>
+        <v>35.0</v>
       </c>
       <c r="R10" t="n">
-        <v>8550000.0</v>
+        <v>900000.0</v>
       </c>
       <c r="S10" t="n">
         <v>0.08</v>
@@ -766,49 +766,49 @@
         <v>0.1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="E11" t="n">
         <v>0.7</v>
       </c>
       <c r="F11" t="n">
-        <v>36.35235289864115</v>
+        <v>28.45887060621136</v>
       </c>
       <c r="G11" t="n">
-        <v>19.72024710465626</v>
+        <v>15.351650585600195</v>
       </c>
       <c r="H11" t="n">
-        <v>12.543011440699166</v>
+        <v>10.47846629169804</v>
       </c>
       <c r="I11" t="n">
-        <v>234.27877118740926</v>
+        <v>195.28487326228222</v>
       </c>
       <c r="J11" t="n">
-        <v>189.40057699696908</v>
+        <v>148.3824076567449</v>
       </c>
       <c r="K11" t="n">
-        <v>111.67769253169617</v>
+        <v>106.04998508782455</v>
       </c>
       <c r="L11" t="n">
         <v>0.0</v>
       </c>
       <c r="M11" t="n">
-        <v>0.9976274717629443</v>
+        <v>0.9488196852860675</v>
       </c>
       <c r="N11" t="n">
-        <v>1.1535886693268032</v>
+        <v>0.9615827159434777</v>
       </c>
       <c r="O11" t="n">
-        <v>0.9326084411330765</v>
+        <v>0.7306349753018117</v>
       </c>
       <c r="P11" t="n">
-        <v>0.549900958026072</v>
+        <v>0.5221901265724481</v>
       </c>
       <c r="Q11" t="n">
-        <v>25.0</v>
+        <v>35.0</v>
       </c>
       <c r="R11" t="n">
-        <v>9450000.0</v>
+        <v>900000.0</v>
       </c>
       <c r="S11" t="n">
         <v>0.08</v>
@@ -831,49 +831,49 @@
         <v>0.1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="E12" t="n">
         <v>0.7</v>
       </c>
       <c r="F12" t="n">
-        <v>36.37736208925489</v>
+        <v>28.468194206537667</v>
       </c>
       <c r="G12" t="n">
-        <v>19.72082422164684</v>
+        <v>15.321681351307507</v>
       </c>
       <c r="H12" t="n">
-        <v>12.542446832545481</v>
+        <v>10.475406341939857</v>
       </c>
       <c r="I12" t="n">
-        <v>234.28174360141236</v>
+        <v>195.27643044466652</v>
       </c>
       <c r="J12" t="n">
-        <v>189.40744060235656</v>
+        <v>148.4084138254848</v>
       </c>
       <c r="K12" t="n">
-        <v>111.67769253169617</v>
+        <v>106.07114746163245</v>
       </c>
       <c r="L12" t="n">
         <v>0.0</v>
       </c>
       <c r="M12" t="n">
-        <v>0.9976882447156205</v>
+        <v>0.9486289471915826</v>
       </c>
       <c r="N12" t="n">
-        <v>1.1536033054933545</v>
+        <v>0.9615411435095379</v>
       </c>
       <c r="O12" t="n">
-        <v>0.9326422375260046</v>
+        <v>0.7307630296766873</v>
       </c>
       <c r="P12" t="n">
-        <v>0.549900958026072</v>
+        <v>0.5222943301010782</v>
       </c>
       <c r="Q12" t="n">
-        <v>25.0</v>
+        <v>35.0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.125E7</v>
+        <v>900000.0</v>
       </c>
       <c r="S12" t="n">
         <v>0.08</v>
@@ -896,49 +896,49 @@
         <v>0.1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="E13" t="n">
         <v>0.7</v>
       </c>
       <c r="F13" t="n">
-        <v>36.32724754227387</v>
+        <v>29.13416263451292</v>
       </c>
       <c r="G13" t="n">
-        <v>19.719062606681838</v>
+        <v>15.526753750239736</v>
       </c>
       <c r="H13" t="n">
-        <v>12.543517691994522</v>
+        <v>10.493498865737985</v>
       </c>
       <c r="I13" t="n">
-        <v>234.2758412568632</v>
+        <v>195.27840153292237</v>
       </c>
       <c r="J13" t="n">
-        <v>189.39552690947448</v>
+        <v>148.30192685288173</v>
       </c>
       <c r="K13" t="n">
-        <v>111.67769253169617</v>
+        <v>105.98649796640085</v>
       </c>
       <c r="L13" t="n">
         <v>0.0</v>
       </c>
       <c r="M13" t="n">
-        <v>0.9975675674123955</v>
+        <v>0.9486734775409391</v>
       </c>
       <c r="N13" t="n">
-        <v>1.1535742423487945</v>
+        <v>0.9615508491481097</v>
       </c>
       <c r="O13" t="n">
-        <v>0.9325835745022533</v>
+        <v>0.7302386878235895</v>
       </c>
       <c r="P13" t="n">
-        <v>0.549900958026072</v>
+        <v>0.5218775159865577</v>
       </c>
       <c r="Q13" t="n">
-        <v>25.0</v>
+        <v>35.0</v>
       </c>
       <c r="R13" t="n">
-        <v>7650000.0</v>
+        <v>900000.0</v>
       </c>
       <c r="S13" t="n">
         <v>0.08</v>
@@ -961,49 +961,49 @@
         <v>0.1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="E14" t="n">
         <v>0.7</v>
       </c>
       <c r="F14" t="n">
-        <v>36.36486944915575</v>
+        <v>28.449483016285107</v>
       </c>
       <c r="G14" t="n">
-        <v>19.720530313127536</v>
+        <v>15.392288194838935</v>
       </c>
       <c r="H14" t="n">
-        <v>12.542730194845157</v>
+        <v>10.483263075215659</v>
       </c>
       <c r="I14" t="n">
-        <v>234.28025208397867</v>
+        <v>195.27736993495424</v>
       </c>
       <c r="J14" t="n">
-        <v>189.40400524188064</v>
+        <v>148.35418052169572</v>
       </c>
       <c r="K14" t="n">
-        <v>111.67769253169617</v>
+        <v>106.02882271401666</v>
       </c>
       <c r="L14" t="n">
         <v>0.0</v>
       </c>
       <c r="M14" t="n">
-        <v>0.9976577496640167</v>
+        <v>0.9486501719290366</v>
       </c>
       <c r="N14" t="n">
-        <v>1.153595961261511</v>
+        <v>0.9615457695597147</v>
       </c>
       <c r="O14" t="n">
-        <v>0.9326253218110199</v>
+        <v>0.7304959848888299</v>
       </c>
       <c r="P14" t="n">
-        <v>0.549900958026072</v>
+        <v>0.5220859230438181</v>
       </c>
       <c r="Q14" t="n">
-        <v>25.0</v>
+        <v>35.0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.035E7</v>
+        <v>900000.0</v>
       </c>
       <c r="S14" t="n">
         <v>0.08</v>
@@ -1026,49 +1026,49 @@
         <v>0.1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="E15" t="n">
         <v>0.7</v>
       </c>
       <c r="F15" t="n">
-        <v>36.389830948775696</v>
+        <v>28.4774638166753</v>
       </c>
       <c r="G15" t="n">
-        <v>19.72112871562885</v>
+        <v>15.294953590407099</v>
       </c>
       <c r="H15" t="n">
-        <v>12.542161354172922</v>
+        <v>10.478897420579605</v>
       </c>
       <c r="I15" t="n">
-        <v>234.28324573971037</v>
+        <v>195.28397982583473</v>
       </c>
       <c r="J15" t="n">
-        <v>189.41088307839755</v>
+        <v>148.4347679942225</v>
       </c>
       <c r="K15" t="n">
-        <v>111.67769253169617</v>
+        <v>106.09230983544036</v>
       </c>
       <c r="L15" t="n">
         <v>0.0</v>
       </c>
       <c r="M15" t="n">
-        <v>0.997718956917756</v>
+        <v>0.9487995009858382</v>
       </c>
       <c r="N15" t="n">
-        <v>1.1536107020223338</v>
+        <v>0.9615783166624102</v>
       </c>
       <c r="O15" t="n">
-        <v>0.9326591882780289</v>
+        <v>0.7308927976035517</v>
       </c>
       <c r="P15" t="n">
-        <v>0.549900958026072</v>
+        <v>0.5223985336297083</v>
       </c>
       <c r="Q15" t="n">
-        <v>25.0</v>
+        <v>35.0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.215E7</v>
+        <v>900000.0</v>
       </c>
       <c r="S15" t="n">
         <v>0.08</v>
@@ -1091,49 +1091,49 @@
         <v>0.1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="E16" t="n">
         <v>0.7</v>
       </c>
       <c r="F16" t="n">
-        <v>36.40227615661695</v>
+        <v>28.775298075243033</v>
       </c>
       <c r="G16" t="n">
-        <v>19.722055968276596</v>
+        <v>15.24550006088727</v>
       </c>
       <c r="H16" t="n">
-        <v>12.541854323807447</v>
+        <v>10.471664524462325</v>
       </c>
       <c r="I16" t="n">
-        <v>234.28475849887255</v>
+        <v>195.2813985221127</v>
       </c>
       <c r="J16" t="n">
-        <v>189.41265058338158</v>
+        <v>148.48313559314437</v>
       </c>
       <c r="K16" t="n">
-        <v>111.67769253169617</v>
+        <v>106.11347220924827</v>
       </c>
       <c r="L16" t="n">
         <v>0.0</v>
       </c>
       <c r="M16" t="n">
-        <v>0.9977498862704234</v>
+        <v>0.9487411847961925</v>
       </c>
       <c r="N16" t="n">
-        <v>1.1536181508484484</v>
+        <v>0.961565606322883</v>
       </c>
       <c r="O16" t="n">
-        <v>0.9326678914725718</v>
+        <v>0.7311309596606431</v>
       </c>
       <c r="P16" t="n">
-        <v>0.549900958026072</v>
+        <v>0.5225027371583385</v>
       </c>
       <c r="Q16" t="n">
-        <v>25.0</v>
+        <v>35.0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.305E7</v>
+        <v>900000.0</v>
       </c>
       <c r="S16" t="n">
         <v>0.08</v>
@@ -1142,71 +1142,6 @@
         <v>39.39</v>
       </c>
       <c r="U16" t="n">
-        <v>1458.0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>30.0</v>
-      </c>
-      <c r="B17" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="F17" t="n">
-        <v>36.414697840747564</v>
-      </c>
-      <c r="G17" t="n">
-        <v>19.72238124211358</v>
-      </c>
-      <c r="H17" t="n">
-        <v>12.541564615497116</v>
-      </c>
-      <c r="I17" t="n">
-        <v>234.28628187889905</v>
-      </c>
-      <c r="J17" t="n">
-        <v>189.41610729055174</v>
-      </c>
-      <c r="K17" t="n">
-        <v>111.67769253169617</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0.9977810327736225</v>
-      </c>
-      <c r="N17" t="n">
-        <v>1.153625651971699</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0.932684912298677</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0.549900958026072</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>25.0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.395E7</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="T17" t="n">
-        <v>39.39</v>
-      </c>
-      <c r="U17" t="n">
         <v>1458.0</v>
       </c>
     </row>

--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -60,7 +60,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:U16"/>
+  <dimension ref="A1:V16"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -169,6 +169,11 @@
           <t>fixed opex</t>
         </is>
       </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>starting capacity</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -187,37 +192,37 @@
         <v>0.7</v>
       </c>
       <c r="F2" t="n">
-        <v>28.41097645332293</v>
+        <v>29.473923819084238</v>
       </c>
       <c r="G2" t="n">
-        <v>16.50237684348026</v>
+        <v>16.63690746801699</v>
       </c>
       <c r="H2" t="n">
-        <v>10.545823234677838</v>
+        <v>10.552466485108072</v>
       </c>
       <c r="I2" t="n">
-        <v>195.2795744295943</v>
+        <v>195.27244450605397</v>
       </c>
       <c r="J2" t="n">
-        <v>147.5371247524124</v>
+        <v>147.44248471645096</v>
       </c>
       <c r="K2" t="n">
-        <v>105.94417321878504</v>
+        <v>105.92301084497716</v>
       </c>
       <c r="L2" t="n">
         <v>0.0</v>
       </c>
       <c r="M2" t="n">
-        <v>0.9486999753389981</v>
+        <v>0.9485388978300666</v>
       </c>
       <c r="N2" t="n">
-        <v>0.9615566244913223</v>
+        <v>0.9615215167478097</v>
       </c>
       <c r="O2" t="n">
-        <v>0.7264728022808785</v>
+        <v>0.7260067947438049</v>
       </c>
       <c r="P2" t="n">
-        <v>0.5216691089292975</v>
+        <v>0.5215649054006675</v>
       </c>
       <c r="Q2" t="n">
         <v>35.0</v>
@@ -233,6 +238,9 @@
       </c>
       <c r="U2" t="n">
         <v>1458.0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>55000.0</v>
       </c>
     </row>
     <row r="3">
@@ -252,37 +260,37 @@
         <v>0.7</v>
       </c>
       <c r="F3" t="n">
-        <v>29.780783977693822</v>
+        <v>28.41097645332293</v>
       </c>
       <c r="G3" t="n">
-        <v>15.58365163678584</v>
+        <v>16.50237684348026</v>
       </c>
       <c r="H3" t="n">
-        <v>10.496061526398798</v>
+        <v>10.545823234677838</v>
       </c>
       <c r="I3" t="n">
-        <v>195.28693645821852</v>
+        <v>195.2795744295943</v>
       </c>
       <c r="J3" t="n">
-        <v>148.27430970996303</v>
+        <v>147.5371247524124</v>
       </c>
       <c r="K3" t="n">
-        <v>105.96533559259294</v>
+        <v>105.94417321878504</v>
       </c>
       <c r="L3" t="n">
         <v>0.0</v>
       </c>
       <c r="M3" t="n">
-        <v>0.9488662965098728</v>
+        <v>0.9486999753389981</v>
       </c>
       <c r="N3" t="n">
-        <v>0.9615928751202679</v>
+        <v>0.9615566244913223</v>
       </c>
       <c r="O3" t="n">
-        <v>0.730102701011858</v>
+        <v>0.7264728022808785</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5217733124579276</v>
+        <v>0.5216691089292975</v>
       </c>
       <c r="Q3" t="n">
         <v>35.0</v>
@@ -298,6 +306,9 @@
       </c>
       <c r="U3" t="n">
         <v>1458.0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>60000.0</v>
       </c>
     </row>
     <row r="4">
@@ -317,37 +328,37 @@
         <v>0.7</v>
       </c>
       <c r="F4" t="n">
-        <v>29.969710495299793</v>
+        <v>29.780783977693822</v>
       </c>
       <c r="G4" t="n">
-        <v>16.964644979867217</v>
+        <v>15.58365163678584</v>
       </c>
       <c r="H4" t="n">
-        <v>10.60809208186763</v>
+        <v>10.496061526398798</v>
       </c>
       <c r="I4" t="n">
-        <v>195.2790628606574</v>
+        <v>195.28693645821852</v>
       </c>
       <c r="J4" t="n">
-        <v>146.95659545461845</v>
+        <v>148.27430970996303</v>
       </c>
       <c r="K4" t="n">
-        <v>105.81719897593761</v>
+        <v>105.96533559259294</v>
       </c>
       <c r="L4" t="n">
         <v>0.0</v>
       </c>
       <c r="M4" t="n">
-        <v>0.9486884180972501</v>
+        <v>0.9488662965098728</v>
       </c>
       <c r="N4" t="n">
-        <v>0.9615541055258771</v>
+        <v>0.9615928751202679</v>
       </c>
       <c r="O4" t="n">
-        <v>0.7236142760185416</v>
+        <v>0.730102701011858</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5210438877575169</v>
+        <v>0.5217733124579276</v>
       </c>
       <c r="Q4" t="n">
         <v>35.0</v>
@@ -363,6 +374,9 @@
       </c>
       <c r="U4" t="n">
         <v>1458.0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>65000.0</v>
       </c>
     </row>
     <row r="5">
@@ -382,37 +396,37 @@
         <v>0.7</v>
       </c>
       <c r="F5" t="n">
-        <v>30.21357635776602</v>
+        <v>29.969710495299793</v>
       </c>
       <c r="G5" t="n">
-        <v>16.694586352223947</v>
+        <v>16.964644979867217</v>
       </c>
       <c r="H5" t="n">
-        <v>10.553937002892145</v>
+        <v>10.60809208186763</v>
       </c>
       <c r="I5" t="n">
-        <v>195.28145804737852</v>
+        <v>195.2790628606574</v>
       </c>
       <c r="J5" t="n">
-        <v>147.3502025453923</v>
+        <v>146.95659545461845</v>
       </c>
       <c r="K5" t="n">
-        <v>105.90184847116923</v>
+        <v>105.81719897593761</v>
       </c>
       <c r="L5" t="n">
         <v>0.0</v>
       </c>
       <c r="M5" t="n">
-        <v>0.9487425295766067</v>
+        <v>0.9486884180972501</v>
       </c>
       <c r="N5" t="n">
-        <v>0.9615658994252918</v>
+        <v>0.9615541055258771</v>
       </c>
       <c r="O5" t="n">
-        <v>0.7255523973335115</v>
+        <v>0.7236142760185416</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5214607018720373</v>
+        <v>0.5210438877575169</v>
       </c>
       <c r="Q5" t="n">
         <v>35.0</v>
@@ -428,6 +442,9 @@
       </c>
       <c r="U5" t="n">
         <v>1458.0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>30000.0</v>
       </c>
     </row>
     <row r="6">
@@ -447,37 +464,37 @@
         <v>0.7</v>
       </c>
       <c r="F6" t="n">
-        <v>29.473923819084238</v>
+        <v>30.21357635776602</v>
       </c>
       <c r="G6" t="n">
-        <v>16.63690746801699</v>
+        <v>16.694586352223947</v>
       </c>
       <c r="H6" t="n">
-        <v>10.552466485108072</v>
+        <v>10.553937002892145</v>
       </c>
       <c r="I6" t="n">
-        <v>195.27244450605397</v>
+        <v>195.28145804737852</v>
       </c>
       <c r="J6" t="n">
-        <v>147.44248471645096</v>
+        <v>147.3502025453923</v>
       </c>
       <c r="K6" t="n">
-        <v>105.92301084497716</v>
+        <v>105.90184847116923</v>
       </c>
       <c r="L6" t="n">
         <v>0.0</v>
       </c>
       <c r="M6" t="n">
-        <v>0.9485388978300666</v>
+        <v>0.9487425295766067</v>
       </c>
       <c r="N6" t="n">
-        <v>0.9615215167478097</v>
+        <v>0.9615658994252918</v>
       </c>
       <c r="O6" t="n">
-        <v>0.7260067947438049</v>
+        <v>0.7255523973335115</v>
       </c>
       <c r="P6" t="n">
-        <v>0.5215649054006675</v>
+        <v>0.5214607018720373</v>
       </c>
       <c r="Q6" t="n">
         <v>35.0</v>
@@ -493,6 +510,9 @@
       </c>
       <c r="U6" t="n">
         <v>1458.0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>50000.0</v>
       </c>
     </row>
     <row r="7">
@@ -559,6 +579,9 @@
       <c r="U7" t="n">
         <v>1458.0</v>
       </c>
+      <c r="V7" t="n">
+        <v>45000.0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -624,6 +647,9 @@
       <c r="U8" t="n">
         <v>1458.0</v>
       </c>
+      <c r="V8" t="n">
+        <v>40000.0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -642,37 +668,37 @@
         <v>0.7</v>
       </c>
       <c r="F9" t="n">
-        <v>28.56673852253458</v>
+        <v>29.867460380569</v>
       </c>
       <c r="G9" t="n">
-        <v>15.478079803252363</v>
+        <v>16.880881194352394</v>
       </c>
       <c r="H9" t="n">
-        <v>10.496878473593608</v>
+        <v>10.605308784976822</v>
       </c>
       <c r="I9" t="n">
-        <v>195.28585880641012</v>
+        <v>195.27341471283276</v>
       </c>
       <c r="J9" t="n">
-        <v>148.32820990917693</v>
+        <v>147.04566799527734</v>
       </c>
       <c r="K9" t="n">
-        <v>106.00766034020876</v>
+        <v>105.83836134974551</v>
       </c>
       <c r="L9" t="n">
         <v>0.0</v>
       </c>
       <c r="M9" t="n">
-        <v>0.9488419504607455</v>
+        <v>0.9485608165070605</v>
       </c>
       <c r="N9" t="n">
-        <v>0.9615875687627634</v>
+        <v>0.9615262940459884</v>
       </c>
       <c r="O9" t="n">
-        <v>0.7303681055927874</v>
+        <v>0.7240528692087459</v>
       </c>
       <c r="P9" t="n">
-        <v>0.521981719515188</v>
+        <v>0.5211480912861469</v>
       </c>
       <c r="Q9" t="n">
         <v>35.0</v>
@@ -688,6 +714,9 @@
       </c>
       <c r="U9" t="n">
         <v>1458.0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>35000.0</v>
       </c>
     </row>
     <row r="10">
@@ -707,37 +736,37 @@
         <v>0.7</v>
       </c>
       <c r="F10" t="n">
-        <v>29.867460380569</v>
+        <v>28.56673852253458</v>
       </c>
       <c r="G10" t="n">
-        <v>16.880881194352394</v>
+        <v>15.478079803252363</v>
       </c>
       <c r="H10" t="n">
-        <v>10.605308784976822</v>
+        <v>10.496878473593608</v>
       </c>
       <c r="I10" t="n">
-        <v>195.27341471283276</v>
+        <v>195.28585880641012</v>
       </c>
       <c r="J10" t="n">
-        <v>147.04566799527734</v>
+        <v>148.32820990917693</v>
       </c>
       <c r="K10" t="n">
-        <v>105.83836134974551</v>
+        <v>106.00766034020876</v>
       </c>
       <c r="L10" t="n">
         <v>0.0</v>
       </c>
       <c r="M10" t="n">
-        <v>0.9485608165070605</v>
+        <v>0.9488419504607455</v>
       </c>
       <c r="N10" t="n">
-        <v>0.9615262940459884</v>
+        <v>0.9615875687627634</v>
       </c>
       <c r="O10" t="n">
-        <v>0.7240528692087459</v>
+        <v>0.7303681055927874</v>
       </c>
       <c r="P10" t="n">
-        <v>0.5211480912861469</v>
+        <v>0.521981719515188</v>
       </c>
       <c r="Q10" t="n">
         <v>35.0</v>
@@ -753,6 +782,9 @@
       </c>
       <c r="U10" t="n">
         <v>1458.0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>75000.0</v>
       </c>
     </row>
     <row r="11">
@@ -772,37 +804,37 @@
         <v>0.7</v>
       </c>
       <c r="F11" t="n">
-        <v>28.45887060621136</v>
+        <v>29.13416263451292</v>
       </c>
       <c r="G11" t="n">
-        <v>15.351650585600195</v>
+        <v>15.526753750239736</v>
       </c>
       <c r="H11" t="n">
-        <v>10.47846629169804</v>
+        <v>10.493498865737985</v>
       </c>
       <c r="I11" t="n">
-        <v>195.28487326228222</v>
+        <v>195.27840153292237</v>
       </c>
       <c r="J11" t="n">
-        <v>148.3824076567449</v>
+        <v>148.30192685288173</v>
       </c>
       <c r="K11" t="n">
-        <v>106.04998508782455</v>
+        <v>105.98649796640085</v>
       </c>
       <c r="L11" t="n">
         <v>0.0</v>
       </c>
       <c r="M11" t="n">
-        <v>0.9488196852860675</v>
+        <v>0.9486734775409391</v>
       </c>
       <c r="N11" t="n">
-        <v>0.9615827159434777</v>
+        <v>0.9615508491481097</v>
       </c>
       <c r="O11" t="n">
-        <v>0.7306349753018117</v>
+        <v>0.7302386878235895</v>
       </c>
       <c r="P11" t="n">
-        <v>0.5221901265724481</v>
+        <v>0.5218775159865577</v>
       </c>
       <c r="Q11" t="n">
         <v>35.0</v>
@@ -818,6 +850,9 @@
       </c>
       <c r="U11" t="n">
         <v>1458.0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>70000.0</v>
       </c>
     </row>
     <row r="12">
@@ -837,37 +872,37 @@
         <v>0.7</v>
       </c>
       <c r="F12" t="n">
-        <v>28.468194206537667</v>
+        <v>28.449483016285107</v>
       </c>
       <c r="G12" t="n">
-        <v>15.321681351307507</v>
+        <v>15.392288194838935</v>
       </c>
       <c r="H12" t="n">
-        <v>10.475406341939857</v>
+        <v>10.483263075215659</v>
       </c>
       <c r="I12" t="n">
-        <v>195.27643044466652</v>
+        <v>195.27736993495424</v>
       </c>
       <c r="J12" t="n">
-        <v>148.4084138254848</v>
+        <v>148.35418052169572</v>
       </c>
       <c r="K12" t="n">
-        <v>106.07114746163245</v>
+        <v>106.02882271401666</v>
       </c>
       <c r="L12" t="n">
         <v>0.0</v>
       </c>
       <c r="M12" t="n">
-        <v>0.9486289471915826</v>
+        <v>0.9486501719290366</v>
       </c>
       <c r="N12" t="n">
-        <v>0.9615411435095379</v>
+        <v>0.9615457695597147</v>
       </c>
       <c r="O12" t="n">
-        <v>0.7307630296766873</v>
+        <v>0.7304959848888299</v>
       </c>
       <c r="P12" t="n">
-        <v>0.5222943301010782</v>
+        <v>0.5220859230438181</v>
       </c>
       <c r="Q12" t="n">
         <v>35.0</v>
@@ -883,6 +918,9 @@
       </c>
       <c r="U12" t="n">
         <v>1458.0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>80000.0</v>
       </c>
     </row>
     <row r="13">
@@ -902,37 +940,37 @@
         <v>0.7</v>
       </c>
       <c r="F13" t="n">
-        <v>29.13416263451292</v>
+        <v>28.45887060621136</v>
       </c>
       <c r="G13" t="n">
-        <v>15.526753750239736</v>
+        <v>15.351650585600195</v>
       </c>
       <c r="H13" t="n">
-        <v>10.493498865737985</v>
+        <v>10.47846629169804</v>
       </c>
       <c r="I13" t="n">
-        <v>195.27840153292237</v>
+        <v>195.28487326228222</v>
       </c>
       <c r="J13" t="n">
-        <v>148.30192685288173</v>
+        <v>148.3824076567449</v>
       </c>
       <c r="K13" t="n">
-        <v>105.98649796640085</v>
+        <v>106.04998508782455</v>
       </c>
       <c r="L13" t="n">
         <v>0.0</v>
       </c>
       <c r="M13" t="n">
-        <v>0.9486734775409391</v>
+        <v>0.9488196852860675</v>
       </c>
       <c r="N13" t="n">
-        <v>0.9615508491481097</v>
+        <v>0.9615827159434777</v>
       </c>
       <c r="O13" t="n">
-        <v>0.7302386878235895</v>
+        <v>0.7306349753018117</v>
       </c>
       <c r="P13" t="n">
-        <v>0.5218775159865577</v>
+        <v>0.5221901265724481</v>
       </c>
       <c r="Q13" t="n">
         <v>35.0</v>
@@ -948,6 +986,9 @@
       </c>
       <c r="U13" t="n">
         <v>1458.0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>85000.0</v>
       </c>
     </row>
     <row r="14">
@@ -967,37 +1008,37 @@
         <v>0.7</v>
       </c>
       <c r="F14" t="n">
-        <v>28.449483016285107</v>
+        <v>28.468194206537667</v>
       </c>
       <c r="G14" t="n">
-        <v>15.392288194838935</v>
+        <v>15.321681351307507</v>
       </c>
       <c r="H14" t="n">
-        <v>10.483263075215659</v>
+        <v>10.475406341939857</v>
       </c>
       <c r="I14" t="n">
-        <v>195.27736993495424</v>
+        <v>195.27643044466652</v>
       </c>
       <c r="J14" t="n">
-        <v>148.35418052169572</v>
+        <v>148.4084138254848</v>
       </c>
       <c r="K14" t="n">
-        <v>106.02882271401666</v>
+        <v>106.07114746163245</v>
       </c>
       <c r="L14" t="n">
         <v>0.0</v>
       </c>
       <c r="M14" t="n">
-        <v>0.9486501719290366</v>
+        <v>0.9486289471915826</v>
       </c>
       <c r="N14" t="n">
-        <v>0.9615457695597147</v>
+        <v>0.9615411435095379</v>
       </c>
       <c r="O14" t="n">
-        <v>0.7304959848888299</v>
+        <v>0.7307630296766873</v>
       </c>
       <c r="P14" t="n">
-        <v>0.5220859230438181</v>
+        <v>0.5222943301010782</v>
       </c>
       <c r="Q14" t="n">
         <v>35.0</v>
@@ -1013,6 +1054,9 @@
       </c>
       <c r="U14" t="n">
         <v>1458.0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>90000.0</v>
       </c>
     </row>
     <row r="15">
@@ -1079,6 +1123,9 @@
       <c r="U15" t="n">
         <v>1458.0</v>
       </c>
+      <c r="V15" t="n">
+        <v>95000.0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1143,6 +1190,9 @@
       </c>
       <c r="U16" t="n">
         <v>1458.0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>100000.0</v>
       </c>
     </row>
   </sheetData>

--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -60,7 +60,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:V16"/>
+  <dimension ref="A1:V20"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -192,37 +192,37 @@
         <v>0.7</v>
       </c>
       <c r="F2" t="n">
-        <v>29.473923819084238</v>
+        <v>29.969710495299793</v>
       </c>
       <c r="G2" t="n">
-        <v>16.63690746801699</v>
+        <v>16.964644979867217</v>
       </c>
       <c r="H2" t="n">
-        <v>10.552466485108072</v>
+        <v>10.60809208186763</v>
       </c>
       <c r="I2" t="n">
-        <v>195.27244450605397</v>
+        <v>195.2790628606574</v>
       </c>
       <c r="J2" t="n">
-        <v>147.44248471645096</v>
+        <v>146.95659545461845</v>
       </c>
       <c r="K2" t="n">
-        <v>105.92301084497716</v>
+        <v>105.81719897593761</v>
       </c>
       <c r="L2" t="n">
         <v>0.0</v>
       </c>
       <c r="M2" t="n">
-        <v>0.9485388978300666</v>
+        <v>0.9486884180972501</v>
       </c>
       <c r="N2" t="n">
-        <v>0.9615215167478097</v>
+        <v>0.9615541055258771</v>
       </c>
       <c r="O2" t="n">
-        <v>0.7260067947438049</v>
+        <v>0.7236142760185416</v>
       </c>
       <c r="P2" t="n">
-        <v>0.5215649054006675</v>
+        <v>0.5210438877575169</v>
       </c>
       <c r="Q2" t="n">
         <v>35.0</v>
@@ -240,7 +240,7 @@
         <v>1458.0</v>
       </c>
       <c r="V2" t="n">
-        <v>55000.0</v>
+        <v>30000.0</v>
       </c>
     </row>
     <row r="3">
@@ -260,37 +260,37 @@
         <v>0.7</v>
       </c>
       <c r="F3" t="n">
-        <v>28.41097645332293</v>
+        <v>29.867460380569</v>
       </c>
       <c r="G3" t="n">
-        <v>16.50237684348026</v>
+        <v>16.880881194352394</v>
       </c>
       <c r="H3" t="n">
-        <v>10.545823234677838</v>
+        <v>10.605308784976822</v>
       </c>
       <c r="I3" t="n">
-        <v>195.2795744295943</v>
+        <v>195.27341471283276</v>
       </c>
       <c r="J3" t="n">
-        <v>147.5371247524124</v>
+        <v>147.04566799527734</v>
       </c>
       <c r="K3" t="n">
-        <v>105.94417321878504</v>
+        <v>105.83836134974551</v>
       </c>
       <c r="L3" t="n">
         <v>0.0</v>
       </c>
       <c r="M3" t="n">
-        <v>0.9486999753389981</v>
+        <v>0.9485608165070605</v>
       </c>
       <c r="N3" t="n">
-        <v>0.9615566244913223</v>
+        <v>0.9615262940459884</v>
       </c>
       <c r="O3" t="n">
-        <v>0.7264728022808785</v>
+        <v>0.7240528692087459</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5216691089292975</v>
+        <v>0.5211480912861469</v>
       </c>
       <c r="Q3" t="n">
         <v>35.0</v>
@@ -308,7 +308,7 @@
         <v>1458.0</v>
       </c>
       <c r="V3" t="n">
-        <v>60000.0</v>
+        <v>35000.0</v>
       </c>
     </row>
     <row r="4">
@@ -328,37 +328,37 @@
         <v>0.7</v>
       </c>
       <c r="F4" t="n">
-        <v>29.780783977693822</v>
+        <v>30.15983371065964</v>
       </c>
       <c r="G4" t="n">
-        <v>15.58365163678584</v>
+        <v>16.796471807428038</v>
       </c>
       <c r="H4" t="n">
-        <v>10.496061526398798</v>
+        <v>10.597017881571995</v>
       </c>
       <c r="I4" t="n">
-        <v>195.28693645821852</v>
+        <v>195.28403909715703</v>
       </c>
       <c r="J4" t="n">
-        <v>148.27430970996303</v>
+        <v>147.16222209971895</v>
       </c>
       <c r="K4" t="n">
-        <v>105.96533559259294</v>
+        <v>105.85952372355341</v>
       </c>
       <c r="L4" t="n">
         <v>0.0</v>
       </c>
       <c r="M4" t="n">
-        <v>0.9488662965098728</v>
+        <v>0.9488008400292219</v>
       </c>
       <c r="N4" t="n">
-        <v>0.9615928751202679</v>
+        <v>0.9615786085144012</v>
       </c>
       <c r="O4" t="n">
-        <v>0.730102701011858</v>
+        <v>0.7246267816190165</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5217733124579276</v>
+        <v>0.521252294814777</v>
       </c>
       <c r="Q4" t="n">
         <v>35.0</v>
@@ -376,7 +376,7 @@
         <v>1458.0</v>
       </c>
       <c r="V4" t="n">
-        <v>65000.0</v>
+        <v>40000.0</v>
       </c>
     </row>
     <row r="5">
@@ -396,37 +396,37 @@
         <v>0.7</v>
       </c>
       <c r="F5" t="n">
-        <v>29.969710495299793</v>
+        <v>30.186549959802534</v>
       </c>
       <c r="G5" t="n">
-        <v>16.964644979867217</v>
+        <v>16.72682945211705</v>
       </c>
       <c r="H5" t="n">
-        <v>10.60809208186763</v>
+        <v>10.568203666168559</v>
       </c>
       <c r="I5" t="n">
-        <v>195.2790628606574</v>
+        <v>195.27467677153132</v>
       </c>
       <c r="J5" t="n">
-        <v>146.95659545461845</v>
+        <v>147.25758584736147</v>
       </c>
       <c r="K5" t="n">
-        <v>105.81719897593761</v>
+        <v>105.88068609736135</v>
       </c>
       <c r="L5" t="n">
         <v>0.0</v>
       </c>
       <c r="M5" t="n">
-        <v>0.9486884180972501</v>
+        <v>0.9485893286320701</v>
       </c>
       <c r="N5" t="n">
-        <v>0.9615541055258771</v>
+        <v>0.9615325084230202</v>
       </c>
       <c r="O5" t="n">
-        <v>0.7236142760185416</v>
+        <v>0.7250963527124079</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5210438877575169</v>
+        <v>0.5213564983434072</v>
       </c>
       <c r="Q5" t="n">
         <v>35.0</v>
@@ -444,7 +444,7 @@
         <v>1458.0</v>
       </c>
       <c r="V5" t="n">
-        <v>30000.0</v>
+        <v>45000.0</v>
       </c>
     </row>
     <row r="6">
@@ -464,37 +464,37 @@
         <v>0.7</v>
       </c>
       <c r="F6" t="n">
-        <v>30.21357635776602</v>
+        <v>32.23811623631403</v>
       </c>
       <c r="G6" t="n">
-        <v>16.694586352223947</v>
+        <v>18.72094144969843</v>
       </c>
       <c r="H6" t="n">
-        <v>10.553937002892145</v>
+        <v>10.665717725715046</v>
       </c>
       <c r="I6" t="n">
-        <v>195.28145804737852</v>
+        <v>195.28014325788018</v>
       </c>
       <c r="J6" t="n">
-        <v>147.3502025453923</v>
+        <v>145.07641354857677</v>
       </c>
       <c r="K6" t="n">
-        <v>105.90184847116923</v>
+        <v>105.73254948070598</v>
       </c>
       <c r="L6" t="n">
         <v>0.0</v>
       </c>
       <c r="M6" t="n">
-        <v>0.9487425295766067</v>
+        <v>0.9487128261701162</v>
       </c>
       <c r="N6" t="n">
-        <v>0.9615658994252918</v>
+        <v>0.9615594254018021</v>
       </c>
       <c r="O6" t="n">
-        <v>0.7255523973335115</v>
+        <v>0.7143562603131921</v>
       </c>
       <c r="P6" t="n">
-        <v>0.5214607018720373</v>
+        <v>0.5206270736429963</v>
       </c>
       <c r="Q6" t="n">
         <v>35.0</v>
@@ -512,7 +512,7 @@
         <v>1458.0</v>
       </c>
       <c r="V6" t="n">
-        <v>50000.0</v>
+        <v>10000.0</v>
       </c>
     </row>
     <row r="7">
@@ -532,37 +532,37 @@
         <v>0.7</v>
       </c>
       <c r="F7" t="n">
-        <v>30.186549959802534</v>
+        <v>31.41376381826182</v>
       </c>
       <c r="G7" t="n">
-        <v>16.72682945211705</v>
+        <v>17.08717255064996</v>
       </c>
       <c r="H7" t="n">
-        <v>10.568203666168559</v>
+        <v>10.61603744024203</v>
       </c>
       <c r="I7" t="n">
-        <v>195.27467677153132</v>
+        <v>195.28487526678177</v>
       </c>
       <c r="J7" t="n">
-        <v>147.25758584736147</v>
+        <v>146.86431536118212</v>
       </c>
       <c r="K7" t="n">
-        <v>105.88068609736135</v>
+        <v>105.7960366021297</v>
       </c>
       <c r="L7" t="n">
         <v>0.0</v>
       </c>
       <c r="M7" t="n">
-        <v>0.9485893286320701</v>
+        <v>0.9488197305712373</v>
       </c>
       <c r="N7" t="n">
-        <v>0.9615325084230202</v>
+        <v>0.9615827258136335</v>
       </c>
       <c r="O7" t="n">
-        <v>0.7250963527124079</v>
+        <v>0.7231598888384607</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5213564983434072</v>
+        <v>0.5209396842288867</v>
       </c>
       <c r="Q7" t="n">
         <v>35.0</v>
@@ -580,7 +580,7 @@
         <v>1458.0</v>
       </c>
       <c r="V7" t="n">
-        <v>45000.0</v>
+        <v>25000.0</v>
       </c>
     </row>
     <row r="8">
@@ -600,37 +600,37 @@
         <v>0.7</v>
       </c>
       <c r="F8" t="n">
-        <v>30.15983371065964</v>
+        <v>29.794254183258097</v>
       </c>
       <c r="G8" t="n">
-        <v>16.796471807428038</v>
+        <v>18.25196204597995</v>
       </c>
       <c r="H8" t="n">
-        <v>10.597017881571995</v>
+        <v>10.62506190474976</v>
       </c>
       <c r="I8" t="n">
-        <v>195.28403909715703</v>
+        <v>195.2721069725043</v>
       </c>
       <c r="J8" t="n">
-        <v>147.16222209971895</v>
+        <v>145.76417424714677</v>
       </c>
       <c r="K8" t="n">
-        <v>105.85952372355341</v>
+        <v>105.7748742283218</v>
       </c>
       <c r="L8" t="n">
         <v>0.0</v>
       </c>
       <c r="M8" t="n">
-        <v>0.9488008400292219</v>
+        <v>0.9485312723537126</v>
       </c>
       <c r="N8" t="n">
-        <v>0.9615786085144012</v>
+        <v>0.9615198547326111</v>
       </c>
       <c r="O8" t="n">
-        <v>0.7246267816190165</v>
+        <v>0.7177427939929506</v>
       </c>
       <c r="P8" t="n">
-        <v>0.521252294814777</v>
+        <v>0.5208354807002566</v>
       </c>
       <c r="Q8" t="n">
         <v>35.0</v>
@@ -648,7 +648,7 @@
         <v>1458.0</v>
       </c>
       <c r="V8" t="n">
-        <v>40000.0</v>
+        <v>20000.0</v>
       </c>
     </row>
     <row r="9">
@@ -668,37 +668,37 @@
         <v>0.7</v>
       </c>
       <c r="F9" t="n">
-        <v>29.867460380569</v>
+        <v>32.654569702980965</v>
       </c>
       <c r="G9" t="n">
-        <v>16.880881194352394</v>
+        <v>18.49316184723999</v>
       </c>
       <c r="H9" t="n">
-        <v>10.605308784976822</v>
+        <v>10.620173289221883</v>
       </c>
       <c r="I9" t="n">
-        <v>195.27341471283276</v>
+        <v>195.27582870035144</v>
       </c>
       <c r="J9" t="n">
-        <v>147.04566799527734</v>
+        <v>145.43507171035014</v>
       </c>
       <c r="K9" t="n">
-        <v>105.83836134974551</v>
+        <v>105.7537118545139</v>
       </c>
       <c r="L9" t="n">
         <v>0.0</v>
       </c>
       <c r="M9" t="n">
-        <v>0.9485608165070605</v>
+        <v>0.9486153527294913</v>
       </c>
       <c r="N9" t="n">
-        <v>0.9615262940459884</v>
+        <v>0.9615381805205305</v>
       </c>
       <c r="O9" t="n">
-        <v>0.7240528692087459</v>
+        <v>0.7161222931017641</v>
       </c>
       <c r="P9" t="n">
-        <v>0.5211480912861469</v>
+        <v>0.5207312771716265</v>
       </c>
       <c r="Q9" t="n">
         <v>35.0</v>
@@ -716,7 +716,7 @@
         <v>1458.0</v>
       </c>
       <c r="V9" t="n">
-        <v>35000.0</v>
+        <v>15000.0</v>
       </c>
     </row>
     <row r="10">
@@ -736,37 +736,37 @@
         <v>0.7</v>
       </c>
       <c r="F10" t="n">
-        <v>28.56673852253458</v>
+        <v>29.473923819084238</v>
       </c>
       <c r="G10" t="n">
-        <v>15.478079803252363</v>
+        <v>16.63690746801699</v>
       </c>
       <c r="H10" t="n">
-        <v>10.496878473593608</v>
+        <v>10.552466485108072</v>
       </c>
       <c r="I10" t="n">
-        <v>195.28585880641012</v>
+        <v>195.27244450605397</v>
       </c>
       <c r="J10" t="n">
-        <v>148.32820990917693</v>
+        <v>147.44248471645096</v>
       </c>
       <c r="K10" t="n">
-        <v>106.00766034020876</v>
+        <v>105.92301084497716</v>
       </c>
       <c r="L10" t="n">
         <v>0.0</v>
       </c>
       <c r="M10" t="n">
-        <v>0.9488419504607455</v>
+        <v>0.9485388978300666</v>
       </c>
       <c r="N10" t="n">
-        <v>0.9615875687627634</v>
+        <v>0.9615215167478097</v>
       </c>
       <c r="O10" t="n">
-        <v>0.7303681055927874</v>
+        <v>0.7260067947438049</v>
       </c>
       <c r="P10" t="n">
-        <v>0.521981719515188</v>
+        <v>0.5215649054006675</v>
       </c>
       <c r="Q10" t="n">
         <v>35.0</v>
@@ -784,7 +784,7 @@
         <v>1458.0</v>
       </c>
       <c r="V10" t="n">
-        <v>75000.0</v>
+        <v>55000.0</v>
       </c>
     </row>
     <row r="11">
@@ -804,37 +804,37 @@
         <v>0.7</v>
       </c>
       <c r="F11" t="n">
-        <v>29.13416263451292</v>
+        <v>29.780783977693822</v>
       </c>
       <c r="G11" t="n">
-        <v>15.526753750239736</v>
+        <v>15.58365163678584</v>
       </c>
       <c r="H11" t="n">
-        <v>10.493498865737985</v>
+        <v>10.496061526398798</v>
       </c>
       <c r="I11" t="n">
-        <v>195.27840153292237</v>
+        <v>195.28693645821852</v>
       </c>
       <c r="J11" t="n">
-        <v>148.30192685288173</v>
+        <v>148.27430970996303</v>
       </c>
       <c r="K11" t="n">
-        <v>105.98649796640085</v>
+        <v>105.96533559259294</v>
       </c>
       <c r="L11" t="n">
         <v>0.0</v>
       </c>
       <c r="M11" t="n">
-        <v>0.9486734775409391</v>
+        <v>0.9488662965098728</v>
       </c>
       <c r="N11" t="n">
-        <v>0.9615508491481097</v>
+        <v>0.9615928751202679</v>
       </c>
       <c r="O11" t="n">
-        <v>0.7302386878235895</v>
+        <v>0.730102701011858</v>
       </c>
       <c r="P11" t="n">
-        <v>0.5218775159865577</v>
+        <v>0.5217733124579276</v>
       </c>
       <c r="Q11" t="n">
         <v>35.0</v>
@@ -852,7 +852,7 @@
         <v>1458.0</v>
       </c>
       <c r="V11" t="n">
-        <v>70000.0</v>
+        <v>65000.0</v>
       </c>
     </row>
     <row r="12">
@@ -872,37 +872,37 @@
         <v>0.7</v>
       </c>
       <c r="F12" t="n">
-        <v>28.449483016285107</v>
+        <v>29.13416263451292</v>
       </c>
       <c r="G12" t="n">
-        <v>15.392288194838935</v>
+        <v>15.526753750239736</v>
       </c>
       <c r="H12" t="n">
-        <v>10.483263075215659</v>
+        <v>10.493498865737985</v>
       </c>
       <c r="I12" t="n">
-        <v>195.27736993495424</v>
+        <v>195.27840153292237</v>
       </c>
       <c r="J12" t="n">
-        <v>148.35418052169572</v>
+        <v>148.30192685288173</v>
       </c>
       <c r="K12" t="n">
-        <v>106.02882271401666</v>
+        <v>105.98649796640085</v>
       </c>
       <c r="L12" t="n">
         <v>0.0</v>
       </c>
       <c r="M12" t="n">
-        <v>0.9486501719290366</v>
+        <v>0.9486734775409391</v>
       </c>
       <c r="N12" t="n">
-        <v>0.9615457695597147</v>
+        <v>0.9615508491481097</v>
       </c>
       <c r="O12" t="n">
-        <v>0.7304959848888299</v>
+        <v>0.7302386878235895</v>
       </c>
       <c r="P12" t="n">
-        <v>0.5220859230438181</v>
+        <v>0.5218775159865577</v>
       </c>
       <c r="Q12" t="n">
         <v>35.0</v>
@@ -920,7 +920,7 @@
         <v>1458.0</v>
       </c>
       <c r="V12" t="n">
-        <v>80000.0</v>
+        <v>70000.0</v>
       </c>
     </row>
     <row r="13">
@@ -940,37 +940,37 @@
         <v>0.7</v>
       </c>
       <c r="F13" t="n">
-        <v>28.45887060621136</v>
+        <v>28.41097645332293</v>
       </c>
       <c r="G13" t="n">
-        <v>15.351650585600195</v>
+        <v>16.50237684348026</v>
       </c>
       <c r="H13" t="n">
-        <v>10.47846629169804</v>
+        <v>10.545823234677838</v>
       </c>
       <c r="I13" t="n">
-        <v>195.28487326228222</v>
+        <v>195.2795744295943</v>
       </c>
       <c r="J13" t="n">
-        <v>148.3824076567449</v>
+        <v>147.5371247524124</v>
       </c>
       <c r="K13" t="n">
-        <v>106.04998508782455</v>
+        <v>105.94417321878504</v>
       </c>
       <c r="L13" t="n">
         <v>0.0</v>
       </c>
       <c r="M13" t="n">
-        <v>0.9488196852860675</v>
+        <v>0.9486999753389981</v>
       </c>
       <c r="N13" t="n">
-        <v>0.9615827159434777</v>
+        <v>0.9615566244913223</v>
       </c>
       <c r="O13" t="n">
-        <v>0.7306349753018117</v>
+        <v>0.7264728022808785</v>
       </c>
       <c r="P13" t="n">
-        <v>0.5221901265724481</v>
+        <v>0.5216691089292975</v>
       </c>
       <c r="Q13" t="n">
         <v>35.0</v>
@@ -988,7 +988,7 @@
         <v>1458.0</v>
       </c>
       <c r="V13" t="n">
-        <v>85000.0</v>
+        <v>60000.0</v>
       </c>
     </row>
     <row r="14">
@@ -1008,37 +1008,37 @@
         <v>0.7</v>
       </c>
       <c r="F14" t="n">
-        <v>28.468194206537667</v>
+        <v>30.21357635776602</v>
       </c>
       <c r="G14" t="n">
-        <v>15.321681351307507</v>
+        <v>16.694586352223947</v>
       </c>
       <c r="H14" t="n">
-        <v>10.475406341939857</v>
+        <v>10.553937002892145</v>
       </c>
       <c r="I14" t="n">
-        <v>195.27643044466652</v>
+        <v>195.28145804737852</v>
       </c>
       <c r="J14" t="n">
-        <v>148.4084138254848</v>
+        <v>147.3502025453923</v>
       </c>
       <c r="K14" t="n">
-        <v>106.07114746163245</v>
+        <v>105.90184847116923</v>
       </c>
       <c r="L14" t="n">
         <v>0.0</v>
       </c>
       <c r="M14" t="n">
-        <v>0.9486289471915826</v>
+        <v>0.9487425295766067</v>
       </c>
       <c r="N14" t="n">
-        <v>0.9615411435095379</v>
+        <v>0.9615658994252918</v>
       </c>
       <c r="O14" t="n">
-        <v>0.7307630296766873</v>
+        <v>0.7255523973335115</v>
       </c>
       <c r="P14" t="n">
-        <v>0.5222943301010782</v>
+        <v>0.5214607018720373</v>
       </c>
       <c r="Q14" t="n">
         <v>35.0</v>
@@ -1056,7 +1056,7 @@
         <v>1458.0</v>
       </c>
       <c r="V14" t="n">
-        <v>90000.0</v>
+        <v>50000.0</v>
       </c>
     </row>
     <row r="15">
@@ -1076,37 +1076,37 @@
         <v>0.7</v>
       </c>
       <c r="F15" t="n">
-        <v>28.4774638166753</v>
+        <v>28.56673852253458</v>
       </c>
       <c r="G15" t="n">
-        <v>15.294953590407099</v>
+        <v>15.478079803252363</v>
       </c>
       <c r="H15" t="n">
-        <v>10.478897420579605</v>
+        <v>10.496878473593608</v>
       </c>
       <c r="I15" t="n">
-        <v>195.28397982583473</v>
+        <v>195.28585880641012</v>
       </c>
       <c r="J15" t="n">
-        <v>148.4347679942225</v>
+        <v>148.32820990917693</v>
       </c>
       <c r="K15" t="n">
-        <v>106.09230983544036</v>
+        <v>106.00766034020876</v>
       </c>
       <c r="L15" t="n">
         <v>0.0</v>
       </c>
       <c r="M15" t="n">
-        <v>0.9487995009858382</v>
+        <v>0.9488419504607455</v>
       </c>
       <c r="N15" t="n">
-        <v>0.9615783166624102</v>
+        <v>0.9615875687627634</v>
       </c>
       <c r="O15" t="n">
-        <v>0.7308927976035517</v>
+        <v>0.7303681055927874</v>
       </c>
       <c r="P15" t="n">
-        <v>0.5223985336297083</v>
+        <v>0.521981719515188</v>
       </c>
       <c r="Q15" t="n">
         <v>35.0</v>
@@ -1124,7 +1124,7 @@
         <v>1458.0</v>
       </c>
       <c r="V15" t="n">
-        <v>95000.0</v>
+        <v>75000.0</v>
       </c>
     </row>
     <row r="16">
@@ -1144,55 +1144,327 @@
         <v>0.7</v>
       </c>
       <c r="F16" t="n">
+        <v>28.449483016285107</v>
+      </c>
+      <c r="G16" t="n">
+        <v>15.392288194838935</v>
+      </c>
+      <c r="H16" t="n">
+        <v>10.483263075215659</v>
+      </c>
+      <c r="I16" t="n">
+        <v>195.27736993495424</v>
+      </c>
+      <c r="J16" t="n">
+        <v>148.35418052169572</v>
+      </c>
+      <c r="K16" t="n">
+        <v>106.02882271401666</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.9486501719290366</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.9615457695597147</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.7304959848888299</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.5220859230438181</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>900000.0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T16" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1458.0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>80000.0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B17" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F17" t="n">
+        <v>28.45887060621136</v>
+      </c>
+      <c r="G17" t="n">
+        <v>15.351650585600195</v>
+      </c>
+      <c r="H17" t="n">
+        <v>10.47846629169804</v>
+      </c>
+      <c r="I17" t="n">
+        <v>195.28487326228222</v>
+      </c>
+      <c r="J17" t="n">
+        <v>148.3824076567449</v>
+      </c>
+      <c r="K17" t="n">
+        <v>106.04998508782455</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.9488196852860675</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.9615827159434777</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.7306349753018117</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.5221901265724481</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>900000.0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T17" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1458.0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>85000.0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B18" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F18" t="n">
+        <v>28.468194206537667</v>
+      </c>
+      <c r="G18" t="n">
+        <v>15.321681351307507</v>
+      </c>
+      <c r="H18" t="n">
+        <v>10.475406341939857</v>
+      </c>
+      <c r="I18" t="n">
+        <v>195.27643044466652</v>
+      </c>
+      <c r="J18" t="n">
+        <v>148.4084138254848</v>
+      </c>
+      <c r="K18" t="n">
+        <v>106.07114746163245</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.9486289471915826</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.9615411435095379</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.7307630296766873</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.5222943301010782</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>900000.0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T18" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1458.0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>90000.0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B19" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F19" t="n">
         <v>28.775298075243033</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G19" t="n">
         <v>15.24550006088727</v>
       </c>
-      <c r="H16" t="n">
+      <c r="H19" t="n">
         <v>10.471664524462325</v>
       </c>
-      <c r="I16" t="n">
+      <c r="I19" t="n">
         <v>195.2813985221127</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J19" t="n">
         <v>148.48313559314437</v>
       </c>
-      <c r="K16" t="n">
+      <c r="K19" t="n">
         <v>106.11347220924827</v>
       </c>
-      <c r="L16" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="M16" t="n">
+      <c r="L19" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M19" t="n">
         <v>0.9487411847961925</v>
       </c>
-      <c r="N16" t="n">
+      <c r="N19" t="n">
         <v>0.961565606322883</v>
       </c>
-      <c r="O16" t="n">
+      <c r="O19" t="n">
         <v>0.7311309596606431</v>
       </c>
-      <c r="P16" t="n">
+      <c r="P19" t="n">
         <v>0.5225027371583385</v>
       </c>
-      <c r="Q16" t="n">
-        <v>35.0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>900000.0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="T16" t="n">
-        <v>39.39</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1458.0</v>
-      </c>
-      <c r="V16" t="n">
+      <c r="Q19" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>900000.0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T19" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1458.0</v>
+      </c>
+      <c r="V19" t="n">
         <v>100000.0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B20" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F20" t="n">
+        <v>28.4774638166753</v>
+      </c>
+      <c r="G20" t="n">
+        <v>15.294953590407099</v>
+      </c>
+      <c r="H20" t="n">
+        <v>10.478897420579605</v>
+      </c>
+      <c r="I20" t="n">
+        <v>195.28397982583473</v>
+      </c>
+      <c r="J20" t="n">
+        <v>148.4347679942225</v>
+      </c>
+      <c r="K20" t="n">
+        <v>106.09230983544036</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.9487995009858382</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.9615783166624102</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.7308927976035517</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.5223985336297083</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>900000.0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T20" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1458.0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>95000.0</v>
       </c>
     </row>
   </sheetData>

--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -60,7 +60,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:V20"/>
+  <dimension ref="A1:V101"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -192,37 +192,37 @@
         <v>0.7</v>
       </c>
       <c r="F2" t="n">
-        <v>29.969710495299793</v>
+        <v>28.41097645332293</v>
       </c>
       <c r="G2" t="n">
-        <v>16.964644979867217</v>
+        <v>16.50237684348026</v>
       </c>
       <c r="H2" t="n">
-        <v>10.60809208186763</v>
+        <v>10.545823234677838</v>
       </c>
       <c r="I2" t="n">
-        <v>195.2790628606574</v>
+        <v>195.2795744295943</v>
       </c>
       <c r="J2" t="n">
-        <v>146.95659545461845</v>
+        <v>147.5371247524124</v>
       </c>
       <c r="K2" t="n">
-        <v>105.81719897593761</v>
+        <v>105.94417321878504</v>
       </c>
       <c r="L2" t="n">
         <v>0.0</v>
       </c>
       <c r="M2" t="n">
-        <v>0.9486884180972501</v>
+        <v>0.9486999753389981</v>
       </c>
       <c r="N2" t="n">
-        <v>0.9615541055258771</v>
+        <v>0.9615566244913223</v>
       </c>
       <c r="O2" t="n">
-        <v>0.7236142760185416</v>
+        <v>0.7264728022808785</v>
       </c>
       <c r="P2" t="n">
-        <v>0.5210438877575169</v>
+        <v>0.5216691089292975</v>
       </c>
       <c r="Q2" t="n">
         <v>35.0</v>
@@ -240,7 +240,7 @@
         <v>1458.0</v>
       </c>
       <c r="V2" t="n">
-        <v>30000.0</v>
+        <v>60000.0</v>
       </c>
     </row>
     <row r="3">
@@ -260,37 +260,37 @@
         <v>0.7</v>
       </c>
       <c r="F3" t="n">
-        <v>29.867460380569</v>
+        <v>29.13416263451292</v>
       </c>
       <c r="G3" t="n">
-        <v>16.880881194352394</v>
+        <v>15.526753750239736</v>
       </c>
       <c r="H3" t="n">
-        <v>10.605308784976822</v>
+        <v>10.493498865737985</v>
       </c>
       <c r="I3" t="n">
-        <v>195.27341471283276</v>
+        <v>195.27840153292237</v>
       </c>
       <c r="J3" t="n">
-        <v>147.04566799527734</v>
+        <v>148.30192685288173</v>
       </c>
       <c r="K3" t="n">
-        <v>105.83836134974551</v>
+        <v>105.98649796640085</v>
       </c>
       <c r="L3" t="n">
         <v>0.0</v>
       </c>
       <c r="M3" t="n">
-        <v>0.9485608165070605</v>
+        <v>0.9486734775409391</v>
       </c>
       <c r="N3" t="n">
-        <v>0.9615262940459884</v>
+        <v>0.9615508491481097</v>
       </c>
       <c r="O3" t="n">
-        <v>0.7240528692087459</v>
+        <v>0.7302386878235895</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5211480912861469</v>
+        <v>0.5218775159865577</v>
       </c>
       <c r="Q3" t="n">
         <v>35.0</v>
@@ -308,7 +308,7 @@
         <v>1458.0</v>
       </c>
       <c r="V3" t="n">
-        <v>35000.0</v>
+        <v>70000.0</v>
       </c>
     </row>
     <row r="4">
@@ -328,37 +328,37 @@
         <v>0.7</v>
       </c>
       <c r="F4" t="n">
-        <v>30.15983371065964</v>
+        <v>28.449483016285107</v>
       </c>
       <c r="G4" t="n">
-        <v>16.796471807428038</v>
+        <v>15.392288194838935</v>
       </c>
       <c r="H4" t="n">
-        <v>10.597017881571995</v>
+        <v>10.483263075215659</v>
       </c>
       <c r="I4" t="n">
-        <v>195.28403909715703</v>
+        <v>195.27736993495424</v>
       </c>
       <c r="J4" t="n">
-        <v>147.16222209971895</v>
+        <v>148.35418052169572</v>
       </c>
       <c r="K4" t="n">
-        <v>105.85952372355341</v>
+        <v>106.02882271401666</v>
       </c>
       <c r="L4" t="n">
         <v>0.0</v>
       </c>
       <c r="M4" t="n">
-        <v>0.9488008400292219</v>
+        <v>0.9486501719290366</v>
       </c>
       <c r="N4" t="n">
-        <v>0.9615786085144012</v>
+        <v>0.9615457695597147</v>
       </c>
       <c r="O4" t="n">
-        <v>0.7246267816190165</v>
+        <v>0.7304959848888299</v>
       </c>
       <c r="P4" t="n">
-        <v>0.521252294814777</v>
+        <v>0.5220859230438181</v>
       </c>
       <c r="Q4" t="n">
         <v>35.0</v>
@@ -376,7 +376,7 @@
         <v>1458.0</v>
       </c>
       <c r="V4" t="n">
-        <v>40000.0</v>
+        <v>80000.0</v>
       </c>
     </row>
     <row r="5">
@@ -396,37 +396,37 @@
         <v>0.7</v>
       </c>
       <c r="F5" t="n">
-        <v>30.186549959802534</v>
+        <v>32.23811623631403</v>
       </c>
       <c r="G5" t="n">
-        <v>16.72682945211705</v>
+        <v>18.72094144969843</v>
       </c>
       <c r="H5" t="n">
-        <v>10.568203666168559</v>
+        <v>10.665717725715046</v>
       </c>
       <c r="I5" t="n">
-        <v>195.27467677153132</v>
+        <v>195.28014325788018</v>
       </c>
       <c r="J5" t="n">
-        <v>147.25758584736147</v>
+        <v>145.07641354857677</v>
       </c>
       <c r="K5" t="n">
-        <v>105.88068609736135</v>
+        <v>105.73254948070598</v>
       </c>
       <c r="L5" t="n">
         <v>0.0</v>
       </c>
       <c r="M5" t="n">
-        <v>0.9485893286320701</v>
+        <v>0.9487128261701162</v>
       </c>
       <c r="N5" t="n">
-        <v>0.9615325084230202</v>
+        <v>0.9615594254018021</v>
       </c>
       <c r="O5" t="n">
-        <v>0.7250963527124079</v>
+        <v>0.7143562603131921</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5213564983434072</v>
+        <v>0.5206270736429963</v>
       </c>
       <c r="Q5" t="n">
         <v>35.0</v>
@@ -444,7 +444,7 @@
         <v>1458.0</v>
       </c>
       <c r="V5" t="n">
-        <v>45000.0</v>
+        <v>10000.0</v>
       </c>
     </row>
     <row r="6">
@@ -464,37 +464,37 @@
         <v>0.7</v>
       </c>
       <c r="F6" t="n">
-        <v>32.23811623631403</v>
+        <v>30.21357635776602</v>
       </c>
       <c r="G6" t="n">
-        <v>18.72094144969843</v>
+        <v>16.694586352223947</v>
       </c>
       <c r="H6" t="n">
-        <v>10.665717725715046</v>
+        <v>10.553937002892145</v>
       </c>
       <c r="I6" t="n">
-        <v>195.28014325788018</v>
+        <v>195.28145804737852</v>
       </c>
       <c r="J6" t="n">
-        <v>145.07641354857677</v>
+        <v>147.3502025453923</v>
       </c>
       <c r="K6" t="n">
-        <v>105.73254948070598</v>
+        <v>105.90184847116923</v>
       </c>
       <c r="L6" t="n">
         <v>0.0</v>
       </c>
       <c r="M6" t="n">
-        <v>0.9487128261701162</v>
+        <v>0.9487425295766067</v>
       </c>
       <c r="N6" t="n">
-        <v>0.9615594254018021</v>
+        <v>0.9615658994252918</v>
       </c>
       <c r="O6" t="n">
-        <v>0.7143562603131921</v>
+        <v>0.7255523973335115</v>
       </c>
       <c r="P6" t="n">
-        <v>0.5206270736429963</v>
+        <v>0.5214607018720373</v>
       </c>
       <c r="Q6" t="n">
         <v>35.0</v>
@@ -512,7 +512,7 @@
         <v>1458.0</v>
       </c>
       <c r="V6" t="n">
-        <v>10000.0</v>
+        <v>50000.0</v>
       </c>
     </row>
     <row r="7">
@@ -532,37 +532,37 @@
         <v>0.7</v>
       </c>
       <c r="F7" t="n">
-        <v>31.41376381826182</v>
+        <v>30.15983371065964</v>
       </c>
       <c r="G7" t="n">
-        <v>17.08717255064996</v>
+        <v>16.796471807428038</v>
       </c>
       <c r="H7" t="n">
-        <v>10.61603744024203</v>
+        <v>10.597017881571995</v>
       </c>
       <c r="I7" t="n">
-        <v>195.28487526678177</v>
+        <v>195.28403909715703</v>
       </c>
       <c r="J7" t="n">
-        <v>146.86431536118212</v>
+        <v>147.16222209971895</v>
       </c>
       <c r="K7" t="n">
-        <v>105.7960366021297</v>
+        <v>105.85952372355341</v>
       </c>
       <c r="L7" t="n">
         <v>0.0</v>
       </c>
       <c r="M7" t="n">
-        <v>0.9488197305712373</v>
+        <v>0.9488008400292219</v>
       </c>
       <c r="N7" t="n">
-        <v>0.9615827258136335</v>
+        <v>0.9615786085144012</v>
       </c>
       <c r="O7" t="n">
-        <v>0.7231598888384607</v>
+        <v>0.7246267816190165</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5209396842288867</v>
+        <v>0.521252294814777</v>
       </c>
       <c r="Q7" t="n">
         <v>35.0</v>
@@ -580,7 +580,7 @@
         <v>1458.0</v>
       </c>
       <c r="V7" t="n">
-        <v>25000.0</v>
+        <v>40000.0</v>
       </c>
     </row>
     <row r="8">
@@ -600,37 +600,37 @@
         <v>0.7</v>
       </c>
       <c r="F8" t="n">
-        <v>29.794254183258097</v>
+        <v>29.969710495299793</v>
       </c>
       <c r="G8" t="n">
-        <v>18.25196204597995</v>
+        <v>16.964644979867217</v>
       </c>
       <c r="H8" t="n">
-        <v>10.62506190474976</v>
+        <v>10.60809208186763</v>
       </c>
       <c r="I8" t="n">
-        <v>195.2721069725043</v>
+        <v>195.2790628606574</v>
       </c>
       <c r="J8" t="n">
-        <v>145.76417424714677</v>
+        <v>146.95659545461845</v>
       </c>
       <c r="K8" t="n">
-        <v>105.7748742283218</v>
+        <v>105.81719897593761</v>
       </c>
       <c r="L8" t="n">
         <v>0.0</v>
       </c>
       <c r="M8" t="n">
-        <v>0.9485312723537126</v>
+        <v>0.9486884180972501</v>
       </c>
       <c r="N8" t="n">
-        <v>0.9615198547326111</v>
+        <v>0.9615541055258771</v>
       </c>
       <c r="O8" t="n">
-        <v>0.7177427939929506</v>
+        <v>0.7236142760185416</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5208354807002566</v>
+        <v>0.5210438877575169</v>
       </c>
       <c r="Q8" t="n">
         <v>35.0</v>
@@ -648,7 +648,7 @@
         <v>1458.0</v>
       </c>
       <c r="V8" t="n">
-        <v>20000.0</v>
+        <v>30000.0</v>
       </c>
     </row>
     <row r="9">
@@ -668,37 +668,37 @@
         <v>0.7</v>
       </c>
       <c r="F9" t="n">
-        <v>32.654569702980965</v>
+        <v>28.775298075243033</v>
       </c>
       <c r="G9" t="n">
-        <v>18.49316184723999</v>
+        <v>15.24550006088727</v>
       </c>
       <c r="H9" t="n">
-        <v>10.620173289221883</v>
+        <v>10.471664524462325</v>
       </c>
       <c r="I9" t="n">
-        <v>195.27582870035144</v>
+        <v>195.2813985221127</v>
       </c>
       <c r="J9" t="n">
-        <v>145.43507171035014</v>
+        <v>148.48313559314437</v>
       </c>
       <c r="K9" t="n">
-        <v>105.7537118545139</v>
+        <v>106.11347220924827</v>
       </c>
       <c r="L9" t="n">
         <v>0.0</v>
       </c>
       <c r="M9" t="n">
-        <v>0.9486153527294913</v>
+        <v>0.9487411847961925</v>
       </c>
       <c r="N9" t="n">
-        <v>0.9615381805205305</v>
+        <v>0.961565606322883</v>
       </c>
       <c r="O9" t="n">
-        <v>0.7161222931017641</v>
+        <v>0.7311309596606431</v>
       </c>
       <c r="P9" t="n">
-        <v>0.5207312771716265</v>
+        <v>0.5225027371583385</v>
       </c>
       <c r="Q9" t="n">
         <v>35.0</v>
@@ -716,7 +716,7 @@
         <v>1458.0</v>
       </c>
       <c r="V9" t="n">
-        <v>15000.0</v>
+        <v>100000.0</v>
       </c>
     </row>
     <row r="10">
@@ -736,37 +736,37 @@
         <v>0.7</v>
       </c>
       <c r="F10" t="n">
-        <v>29.473923819084238</v>
+        <v>28.468194206537667</v>
       </c>
       <c r="G10" t="n">
-        <v>16.63690746801699</v>
+        <v>15.321681351307507</v>
       </c>
       <c r="H10" t="n">
-        <v>10.552466485108072</v>
+        <v>10.475406341939857</v>
       </c>
       <c r="I10" t="n">
-        <v>195.27244450605397</v>
+        <v>195.27643044466652</v>
       </c>
       <c r="J10" t="n">
-        <v>147.44248471645096</v>
+        <v>148.4084138254848</v>
       </c>
       <c r="K10" t="n">
-        <v>105.92301084497716</v>
+        <v>106.07114746163245</v>
       </c>
       <c r="L10" t="n">
         <v>0.0</v>
       </c>
       <c r="M10" t="n">
-        <v>0.9485388978300666</v>
+        <v>0.9486289471915826</v>
       </c>
       <c r="N10" t="n">
-        <v>0.9615215167478097</v>
+        <v>0.9615411435095379</v>
       </c>
       <c r="O10" t="n">
-        <v>0.7260067947438049</v>
+        <v>0.7307630296766873</v>
       </c>
       <c r="P10" t="n">
-        <v>0.5215649054006675</v>
+        <v>0.5222943301010782</v>
       </c>
       <c r="Q10" t="n">
         <v>35.0</v>
@@ -784,7 +784,7 @@
         <v>1458.0</v>
       </c>
       <c r="V10" t="n">
-        <v>55000.0</v>
+        <v>90000.0</v>
       </c>
     </row>
     <row r="11">
@@ -804,37 +804,37 @@
         <v>0.7</v>
       </c>
       <c r="F11" t="n">
-        <v>29.780783977693822</v>
+        <v>28.79375618817886</v>
       </c>
       <c r="G11" t="n">
-        <v>15.58365163678584</v>
+        <v>15.207651068234746</v>
       </c>
       <c r="H11" t="n">
-        <v>10.496061526398798</v>
+        <v>10.47162401852356</v>
       </c>
       <c r="I11" t="n">
-        <v>195.28693645821852</v>
+        <v>195.28125803601674</v>
       </c>
       <c r="J11" t="n">
-        <v>148.27430970996303</v>
+        <v>148.53802527512065</v>
       </c>
       <c r="K11" t="n">
-        <v>105.96533559259294</v>
+        <v>106.15579695686408</v>
       </c>
       <c r="L11" t="n">
         <v>0.0</v>
       </c>
       <c r="M11" t="n">
-        <v>0.9488662965098728</v>
+        <v>0.9487380109682745</v>
       </c>
       <c r="N11" t="n">
-        <v>0.9615928751202679</v>
+        <v>0.9615649145693465</v>
       </c>
       <c r="O11" t="n">
-        <v>0.730102701011858</v>
+        <v>0.731401236454694</v>
       </c>
       <c r="P11" t="n">
-        <v>0.5217733124579276</v>
+        <v>0.5227111442155987</v>
       </c>
       <c r="Q11" t="n">
         <v>35.0</v>
@@ -852,7 +852,7 @@
         <v>1458.0</v>
       </c>
       <c r="V11" t="n">
-        <v>65000.0</v>
+        <v>110000.0</v>
       </c>
     </row>
     <row r="12">
@@ -872,37 +872,37 @@
         <v>0.7</v>
       </c>
       <c r="F12" t="n">
-        <v>29.13416263451292</v>
+        <v>28.8120895518146</v>
       </c>
       <c r="G12" t="n">
-        <v>15.526753750239736</v>
+        <v>15.175844021121124</v>
       </c>
       <c r="H12" t="n">
-        <v>10.493498865737985</v>
+        <v>10.471434589075661</v>
       </c>
       <c r="I12" t="n">
-        <v>195.27840153292237</v>
+        <v>195.28121767969796</v>
       </c>
       <c r="J12" t="n">
-        <v>148.30192685288173</v>
+        <v>148.59490093923628</v>
       </c>
       <c r="K12" t="n">
-        <v>105.98649796640085</v>
+        <v>106.19812170447989</v>
       </c>
       <c r="L12" t="n">
         <v>0.0</v>
       </c>
       <c r="M12" t="n">
-        <v>0.9486734775409391</v>
+        <v>0.9487370992480778</v>
       </c>
       <c r="N12" t="n">
-        <v>0.9615508491481097</v>
+        <v>0.9615647158548328</v>
       </c>
       <c r="O12" t="n">
-        <v>0.7302386878235895</v>
+        <v>0.7316812922247997</v>
       </c>
       <c r="P12" t="n">
-        <v>0.5218775159865577</v>
+        <v>0.5229195512728589</v>
       </c>
       <c r="Q12" t="n">
         <v>35.0</v>
@@ -920,7 +920,7 @@
         <v>1458.0</v>
       </c>
       <c r="V12" t="n">
-        <v>70000.0</v>
+        <v>120000.0</v>
       </c>
     </row>
     <row r="13">
@@ -940,37 +940,37 @@
         <v>0.7</v>
       </c>
       <c r="F13" t="n">
-        <v>28.41097645332293</v>
+        <v>27.85262369048917</v>
       </c>
       <c r="G13" t="n">
-        <v>16.50237684348026</v>
+        <v>14.409107370315875</v>
       </c>
       <c r="H13" t="n">
-        <v>10.545823234677838</v>
+        <v>10.468561620352451</v>
       </c>
       <c r="I13" t="n">
-        <v>195.2795744295943</v>
+        <v>195.27432516004131</v>
       </c>
       <c r="J13" t="n">
-        <v>147.5371247524124</v>
+        <v>149.07627345067584</v>
       </c>
       <c r="K13" t="n">
-        <v>105.94417321878504</v>
+        <v>106.2827711997115</v>
       </c>
       <c r="L13" t="n">
         <v>0.0</v>
       </c>
       <c r="M13" t="n">
-        <v>0.9486999753389981</v>
+        <v>0.9485813851102923</v>
       </c>
       <c r="N13" t="n">
-        <v>0.9615566244913223</v>
+        <v>0.9615307770880435</v>
       </c>
       <c r="O13" t="n">
-        <v>0.7264728022808785</v>
+        <v>0.734051570471128</v>
       </c>
       <c r="P13" t="n">
-        <v>0.5216691089292975</v>
+        <v>0.5233363653873795</v>
       </c>
       <c r="Q13" t="n">
         <v>35.0</v>
@@ -988,7 +988,7 @@
         <v>1458.0</v>
       </c>
       <c r="V13" t="n">
-        <v>60000.0</v>
+        <v>140000.0</v>
       </c>
     </row>
     <row r="14">
@@ -1008,37 +1008,37 @@
         <v>0.7</v>
       </c>
       <c r="F14" t="n">
-        <v>30.21357635776602</v>
+        <v>28.830326419124997</v>
       </c>
       <c r="G14" t="n">
-        <v>16.694586352223947</v>
+        <v>15.150825682172925</v>
       </c>
       <c r="H14" t="n">
-        <v>10.553937002892145</v>
+        <v>10.471329609378344</v>
       </c>
       <c r="I14" t="n">
-        <v>195.28145804737852</v>
+        <v>195.2812774531565</v>
       </c>
       <c r="J14" t="n">
-        <v>147.3502025453923</v>
+        <v>148.6499455404263</v>
       </c>
       <c r="K14" t="n">
-        <v>105.90184847116923</v>
+        <v>106.2404464520957</v>
       </c>
       <c r="L14" t="n">
         <v>0.0</v>
       </c>
       <c r="M14" t="n">
-        <v>0.9487425295766067</v>
+        <v>0.9487384496356026</v>
       </c>
       <c r="N14" t="n">
-        <v>0.9615658994252918</v>
+        <v>0.9615650101793426</v>
       </c>
       <c r="O14" t="n">
-        <v>0.7255523973335115</v>
+        <v>0.7319523318410591</v>
       </c>
       <c r="P14" t="n">
-        <v>0.5214607018720373</v>
+        <v>0.5231279583301192</v>
       </c>
       <c r="Q14" t="n">
         <v>35.0</v>
@@ -1056,7 +1056,7 @@
         <v>1458.0</v>
       </c>
       <c r="V14" t="n">
-        <v>50000.0</v>
+        <v>130000.0</v>
       </c>
     </row>
     <row r="15">
@@ -1076,37 +1076,37 @@
         <v>0.7</v>
       </c>
       <c r="F15" t="n">
-        <v>28.56673852253458</v>
+        <v>29.794254183258097</v>
       </c>
       <c r="G15" t="n">
-        <v>15.478079803252363</v>
+        <v>18.25196204597995</v>
       </c>
       <c r="H15" t="n">
-        <v>10.496878473593608</v>
+        <v>10.62506190474976</v>
       </c>
       <c r="I15" t="n">
-        <v>195.28585880641012</v>
+        <v>195.2721069725043</v>
       </c>
       <c r="J15" t="n">
-        <v>148.32820990917693</v>
+        <v>145.76417424714677</v>
       </c>
       <c r="K15" t="n">
-        <v>106.00766034020876</v>
+        <v>105.7748742283218</v>
       </c>
       <c r="L15" t="n">
         <v>0.0</v>
       </c>
       <c r="M15" t="n">
-        <v>0.9488419504607455</v>
+        <v>0.9485312723537126</v>
       </c>
       <c r="N15" t="n">
-        <v>0.9615875687627634</v>
+        <v>0.9615198547326111</v>
       </c>
       <c r="O15" t="n">
-        <v>0.7303681055927874</v>
+        <v>0.7177427939929506</v>
       </c>
       <c r="P15" t="n">
-        <v>0.521981719515188</v>
+        <v>0.5208354807002566</v>
       </c>
       <c r="Q15" t="n">
         <v>35.0</v>
@@ -1124,7 +1124,7 @@
         <v>1458.0</v>
       </c>
       <c r="V15" t="n">
-        <v>75000.0</v>
+        <v>20000.0</v>
       </c>
     </row>
     <row r="16">
@@ -1144,37 +1144,37 @@
         <v>0.7</v>
       </c>
       <c r="F16" t="n">
-        <v>28.449483016285107</v>
+        <v>26.194580127768184</v>
       </c>
       <c r="G16" t="n">
-        <v>15.392288194838935</v>
+        <v>14.24129905764831</v>
       </c>
       <c r="H16" t="n">
-        <v>10.483263075215659</v>
+        <v>10.460184205025701</v>
       </c>
       <c r="I16" t="n">
-        <v>195.27736993495424</v>
+        <v>195.28155818890463</v>
       </c>
       <c r="J16" t="n">
-        <v>148.35418052169572</v>
+        <v>149.12561317248486</v>
       </c>
       <c r="K16" t="n">
-        <v>106.02882271401666</v>
+        <v>106.40974544255893</v>
       </c>
       <c r="L16" t="n">
         <v>0.0</v>
       </c>
       <c r="M16" t="n">
-        <v>0.9486501719290366</v>
+        <v>0.948744791949754</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9615457695597147</v>
+        <v>0.9615663925221664</v>
       </c>
       <c r="O16" t="n">
-        <v>0.7304959848888299</v>
+        <v>0.7342945192613155</v>
       </c>
       <c r="P16" t="n">
-        <v>0.5220859230438181</v>
+        <v>0.5239615865591601</v>
       </c>
       <c r="Q16" t="n">
         <v>35.0</v>
@@ -1192,7 +1192,7 @@
         <v>1458.0</v>
       </c>
       <c r="V16" t="n">
-        <v>80000.0</v>
+        <v>170000.0</v>
       </c>
     </row>
     <row r="17">
@@ -1212,37 +1212,37 @@
         <v>0.7</v>
       </c>
       <c r="F17" t="n">
-        <v>28.45887060621136</v>
+        <v>26.67640237857833</v>
       </c>
       <c r="G17" t="n">
-        <v>15.351650585600195</v>
+        <v>14.287815320411536</v>
       </c>
       <c r="H17" t="n">
-        <v>10.47846629169804</v>
+        <v>10.461370186921675</v>
       </c>
       <c r="I17" t="n">
-        <v>195.28487326228222</v>
+        <v>195.27916165088973</v>
       </c>
       <c r="J17" t="n">
-        <v>148.3824076567449</v>
+        <v>149.1090895931348</v>
       </c>
       <c r="K17" t="n">
-        <v>106.04998508782455</v>
+        <v>106.36742069494312</v>
       </c>
       <c r="L17" t="n">
         <v>0.0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.9488196852860675</v>
+        <v>0.9486906499422956</v>
       </c>
       <c r="N17" t="n">
-        <v>0.9615827159434777</v>
+        <v>0.961554591968981</v>
       </c>
       <c r="O17" t="n">
-        <v>0.7306349753018117</v>
+        <v>0.7342131571565956</v>
       </c>
       <c r="P17" t="n">
-        <v>0.5221901265724481</v>
+        <v>0.5237531795018999</v>
       </c>
       <c r="Q17" t="n">
         <v>35.0</v>
@@ -1260,7 +1260,7 @@
         <v>1458.0</v>
       </c>
       <c r="V17" t="n">
-        <v>85000.0</v>
+        <v>160000.0</v>
       </c>
     </row>
     <row r="18">
@@ -1280,37 +1280,37 @@
         <v>0.7</v>
       </c>
       <c r="F18" t="n">
-        <v>28.468194206537667</v>
+        <v>27.583974920867483</v>
       </c>
       <c r="G18" t="n">
-        <v>15.321681351307507</v>
+        <v>14.249906939890394</v>
       </c>
       <c r="H18" t="n">
-        <v>10.475406341939857</v>
+        <v>10.464944337370575</v>
       </c>
       <c r="I18" t="n">
-        <v>195.27643044466652</v>
+        <v>195.2853073653158</v>
       </c>
       <c r="J18" t="n">
-        <v>148.4084138254848</v>
+        <v>149.27418647080404</v>
       </c>
       <c r="K18" t="n">
-        <v>106.07114746163245</v>
+        <v>106.49439493779056</v>
       </c>
       <c r="L18" t="n">
         <v>0.0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.9486289471915826</v>
+        <v>0.948829492436856</v>
       </c>
       <c r="N18" t="n">
-        <v>0.9615411435095379</v>
+        <v>0.961584853466815</v>
       </c>
       <c r="O18" t="n">
-        <v>0.7307630296766873</v>
+        <v>0.7350260941822391</v>
       </c>
       <c r="P18" t="n">
-        <v>0.5222943301010782</v>
+        <v>0.5243784006736807</v>
       </c>
       <c r="Q18" t="n">
         <v>35.0</v>
@@ -1328,7 +1328,7 @@
         <v>1458.0</v>
       </c>
       <c r="V18" t="n">
-        <v>90000.0</v>
+        <v>190000.0</v>
       </c>
     </row>
     <row r="19">
@@ -1348,37 +1348,37 @@
         <v>0.7</v>
       </c>
       <c r="F19" t="n">
-        <v>28.775298075243033</v>
+        <v>27.224364985266973</v>
       </c>
       <c r="G19" t="n">
-        <v>15.24550006088727</v>
+        <v>14.350097189695918</v>
       </c>
       <c r="H19" t="n">
-        <v>10.471664524462325</v>
+        <v>10.467458005728085</v>
       </c>
       <c r="I19" t="n">
-        <v>195.2813985221127</v>
+        <v>195.27675064126865</v>
       </c>
       <c r="J19" t="n">
-        <v>148.48313559314437</v>
+        <v>149.09091493583358</v>
       </c>
       <c r="K19" t="n">
-        <v>106.11347220924827</v>
+        <v>106.32509594732731</v>
       </c>
       <c r="L19" t="n">
         <v>0.0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.9487411847961925</v>
+        <v>0.9486361809958084</v>
       </c>
       <c r="N19" t="n">
-        <v>0.961565606322883</v>
+        <v>0.9615427201576068</v>
       </c>
       <c r="O19" t="n">
-        <v>0.7311309596606431</v>
+        <v>0.7341236651440446</v>
       </c>
       <c r="P19" t="n">
-        <v>0.5225027371583385</v>
+        <v>0.5235447724446397</v>
       </c>
       <c r="Q19" t="n">
         <v>35.0</v>
@@ -1396,7 +1396,7 @@
         <v>1458.0</v>
       </c>
       <c r="V19" t="n">
-        <v>100000.0</v>
+        <v>150000.0</v>
       </c>
     </row>
     <row r="20">
@@ -1416,37 +1416,37 @@
         <v>0.7</v>
       </c>
       <c r="F20" t="n">
-        <v>28.4774638166753</v>
+        <v>27.039041669581863</v>
       </c>
       <c r="G20" t="n">
-        <v>15.294953590407099</v>
+        <v>14.183976193675349</v>
       </c>
       <c r="H20" t="n">
-        <v>10.478897420579605</v>
+        <v>10.459287918346016</v>
       </c>
       <c r="I20" t="n">
-        <v>195.28397982583473</v>
+        <v>195.2853073653158</v>
       </c>
       <c r="J20" t="n">
-        <v>148.4347679942225</v>
+        <v>149.28237304374125</v>
       </c>
       <c r="K20" t="n">
-        <v>106.09230983544036</v>
+        <v>106.53671968540637</v>
       </c>
       <c r="L20" t="n">
         <v>0.0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.9487995009858382</v>
+        <v>0.948829492436856</v>
       </c>
       <c r="N20" t="n">
-        <v>0.9615783166624102</v>
+        <v>0.961584853466815</v>
       </c>
       <c r="O20" t="n">
-        <v>0.7308927976035517</v>
+        <v>0.7350664048673818</v>
       </c>
       <c r="P20" t="n">
-        <v>0.5223985336297083</v>
+        <v>0.5245868077309409</v>
       </c>
       <c r="Q20" t="n">
         <v>35.0</v>
@@ -1464,7 +1464,5515 @@
         <v>1458.0</v>
       </c>
       <c r="V20" t="n">
-        <v>95000.0</v>
+        <v>200000.0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B21" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F21" t="n">
+        <v>26.473811406174654</v>
+      </c>
+      <c r="G21" t="n">
+        <v>14.144476346920332</v>
+      </c>
+      <c r="H21" t="n">
+        <v>10.458779275015209</v>
+      </c>
+      <c r="I21" t="n">
+        <v>195.2853073653158</v>
+      </c>
+      <c r="J21" t="n">
+        <v>149.28861297491167</v>
+      </c>
+      <c r="K21" t="n">
+        <v>106.57904443302215</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.948829492436856</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.961584853466815</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.7350971302884651</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.5247952147882011</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>900000.0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T21" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1458.0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>210000.0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B22" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F22" t="n">
+        <v>25.767885143491505</v>
+      </c>
+      <c r="G22" t="n">
+        <v>14.200071278443906</v>
+      </c>
+      <c r="H22" t="n">
+        <v>10.464736989423136</v>
+      </c>
+      <c r="I22" t="n">
+        <v>195.28394025531327</v>
+      </c>
+      <c r="J22" t="n">
+        <v>149.1421235376649</v>
+      </c>
+      <c r="K22" t="n">
+        <v>106.45207019017475</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.948798607018184</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.9615781218171626</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.7343758162994616</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0.5241699936164205</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>900000.0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T22" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1458.0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>180000.0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B23" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F23" t="n">
+        <v>25.960507375322106</v>
+      </c>
+      <c r="G23" t="n">
+        <v>14.108420714393068</v>
+      </c>
+      <c r="H23" t="n">
+        <v>10.458270631684403</v>
+      </c>
+      <c r="I23" t="n">
+        <v>195.2853073653158</v>
+      </c>
+      <c r="J23" t="n">
+        <v>149.2948529060821</v>
+      </c>
+      <c r="K23" t="n">
+        <v>106.62136918063798</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.948829492436856</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.961584853466815</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.7351278557095483</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0.5250036218454615</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>900000.0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T23" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1458.0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>220000.0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B24" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F24" t="n">
+        <v>25.06371489500365</v>
+      </c>
+      <c r="G24" t="n">
+        <v>14.044919984907937</v>
+      </c>
+      <c r="H24" t="n">
+        <v>10.45725334502279</v>
+      </c>
+      <c r="I24" t="n">
+        <v>195.2853073653158</v>
+      </c>
+      <c r="J24" t="n">
+        <v>149.30733276842295</v>
+      </c>
+      <c r="K24" t="n">
+        <v>106.70601867586957</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.948829492436856</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0.961584853466815</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.7351893065517147</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.5254204359599818</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>900000.0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T24" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1458.0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>240000.0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B25" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F25" t="n">
+        <v>25.492356590169255</v>
+      </c>
+      <c r="G25" t="n">
+        <v>14.075360050759505</v>
+      </c>
+      <c r="H25" t="n">
+        <v>10.457761988353596</v>
+      </c>
+      <c r="I25" t="n">
+        <v>195.2853073653158</v>
+      </c>
+      <c r="J25" t="n">
+        <v>149.30109283725253</v>
+      </c>
+      <c r="K25" t="n">
+        <v>106.66369392825379</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.948829492436856</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0.961584853466815</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.7351585811306314</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0.5252120289027217</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>900000.0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T25" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1458.0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>230000.0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B26" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F26" t="n">
+        <v>24.306723810024685</v>
+      </c>
+      <c r="G26" t="n">
+        <v>13.990692139882157</v>
+      </c>
+      <c r="H26" t="n">
+        <v>10.456236058361181</v>
+      </c>
+      <c r="I26" t="n">
+        <v>195.2853073653158</v>
+      </c>
+      <c r="J26" t="n">
+        <v>149.3198126307638</v>
+      </c>
+      <c r="K26" t="n">
+        <v>106.79066817110122</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.948829492436856</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0.961584853466815</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.735250757393881</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0.5258372500745023</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>900000.0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T26" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1458.0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>260000.0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B27" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F27" t="n">
+        <v>24.669841199026827</v>
+      </c>
+      <c r="G27" t="n">
+        <v>14.016786045104519</v>
+      </c>
+      <c r="H27" t="n">
+        <v>10.456744701691985</v>
+      </c>
+      <c r="I27" t="n">
+        <v>195.2853073653158</v>
+      </c>
+      <c r="J27" t="n">
+        <v>149.31357269959338</v>
+      </c>
+      <c r="K27" t="n">
+        <v>106.74834342348541</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.948829492436856</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0.961584853466815</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0.7352200319727978</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0.5256288430172421</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>900000.0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T27" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1458.0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>250000.0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B28" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F28" t="n">
+        <v>23.97094536055559</v>
+      </c>
+      <c r="G28" t="n">
+        <v>13.944230642103012</v>
+      </c>
+      <c r="H28" t="n">
+        <v>10.455727415030374</v>
+      </c>
+      <c r="I28" t="n">
+        <v>195.2853073653158</v>
+      </c>
+      <c r="J28" t="n">
+        <v>149.32605256193423</v>
+      </c>
+      <c r="K28" t="n">
+        <v>106.832992918717</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.948829492436856</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.961584853466815</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.7352814828149642</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0.5260456571317625</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>900000.0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T28" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1458.0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>270000.0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B29" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F29" t="n">
+        <v>23.65957667852673</v>
+      </c>
+      <c r="G29" t="n">
+        <v>13.886796271046515</v>
+      </c>
+      <c r="H29" t="n">
+        <v>10.455218771699569</v>
+      </c>
+      <c r="I29" t="n">
+        <v>195.2853073653158</v>
+      </c>
+      <c r="J29" t="n">
+        <v>149.33229249310466</v>
+      </c>
+      <c r="K29" t="n">
+        <v>106.87531766633282</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.948829492436856</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0.961584853466815</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0.7353122082360474</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0.5262540641890229</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>900000.0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T29" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1458.0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>280000.0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B30" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F30" t="n">
+        <v>23.10030470981358</v>
+      </c>
+      <c r="G30" t="n">
+        <v>13.783058411815233</v>
+      </c>
+      <c r="H30" t="n">
+        <v>10.454201485037956</v>
+      </c>
+      <c r="I30" t="n">
+        <v>195.2853073653158</v>
+      </c>
+      <c r="J30" t="n">
+        <v>149.3447723554455</v>
+      </c>
+      <c r="K30" t="n">
+        <v>106.95996716156442</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.948829492436856</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0.961584853466815</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0.7353736590782137</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0.5266708783035432</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="R30" t="n">
+        <v>900000.0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T30" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1458.0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>300000.0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B31" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F31" t="n">
+        <v>22.848306881494178</v>
+      </c>
+      <c r="G31" t="n">
+        <v>13.736036802164207</v>
+      </c>
+      <c r="H31" t="n">
+        <v>10.45369284170715</v>
+      </c>
+      <c r="I31" t="n">
+        <v>195.2853073653158</v>
+      </c>
+      <c r="J31" t="n">
+        <v>149.35101228661597</v>
+      </c>
+      <c r="K31" t="n">
+        <v>107.00229190918024</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.948829492436856</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0.961584853466815</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0.735404384499297</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0.5268792853608035</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>900000.0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T31" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1458.0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>310000.0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B32" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F32" t="n">
+        <v>23.370092615582205</v>
+      </c>
+      <c r="G32" t="n">
+        <v>13.833200135466468</v>
+      </c>
+      <c r="H32" t="n">
+        <v>10.454710128368761</v>
+      </c>
+      <c r="I32" t="n">
+        <v>195.2853073653158</v>
+      </c>
+      <c r="J32" t="n">
+        <v>149.3385324242751</v>
+      </c>
+      <c r="K32" t="n">
+        <v>106.91764241394861</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.948829492436856</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0.961584853466815</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0.7353429336571305</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0.526462471246283</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="R32" t="n">
+        <v>900000.0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T32" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1458.0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>290000.0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B33" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F33" t="n">
+        <v>22.63307837414839</v>
+      </c>
+      <c r="G33" t="n">
+        <v>13.69184279582588</v>
+      </c>
+      <c r="H33" t="n">
+        <v>10.453184198376345</v>
+      </c>
+      <c r="I33" t="n">
+        <v>195.2853073653158</v>
+      </c>
+      <c r="J33" t="n">
+        <v>149.35725221778637</v>
+      </c>
+      <c r="K33" t="n">
+        <v>107.04461665679605</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.948829492436856</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0.961584853466815</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0.7354351099203801</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0.5270876924180637</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="R33" t="n">
+        <v>900000.0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T33" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1458.0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>320000.0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B34" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F34" t="n">
+        <v>22.61248636499834</v>
+      </c>
+      <c r="G34" t="n">
+        <v>13.650219337953635</v>
+      </c>
+      <c r="H34" t="n">
+        <v>10.452675555045538</v>
+      </c>
+      <c r="I34" t="n">
+        <v>195.2853073653158</v>
+      </c>
+      <c r="J34" t="n">
+        <v>149.3634921489568</v>
+      </c>
+      <c r="K34" t="n">
+        <v>107.08694140441186</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.948829492436856</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0.961584853466815</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0.7354658353414633</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0.527296099475324</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="R34" t="n">
+        <v>900000.0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T34" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1458.0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>330000.0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B35" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F35" t="n">
+        <v>22.591894355848286</v>
+      </c>
+      <c r="G35" t="n">
+        <v>13.610939615447531</v>
+      </c>
+      <c r="H35" t="n">
+        <v>10.45216691171473</v>
+      </c>
+      <c r="I35" t="n">
+        <v>195.2853073653158</v>
+      </c>
+      <c r="J35" t="n">
+        <v>149.36973208012722</v>
+      </c>
+      <c r="K35" t="n">
+        <v>107.12926615202767</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.948829492436856</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0.961584853466815</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0.7354965607625464</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0.5275045065325843</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>900000.0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T35" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1458.0</v>
+      </c>
+      <c r="V35" t="n">
+        <v>340000.0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B36" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F36" t="n">
+        <v>22.571302346698232</v>
+      </c>
+      <c r="G36" t="n">
+        <v>13.573802736704748</v>
+      </c>
+      <c r="H36" t="n">
+        <v>10.451658268383927</v>
+      </c>
+      <c r="I36" t="n">
+        <v>195.2853073653158</v>
+      </c>
+      <c r="J36" t="n">
+        <v>149.37597201129765</v>
+      </c>
+      <c r="K36" t="n">
+        <v>107.17159089964348</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.948829492436856</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0.961584853466815</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0.7355272861836297</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0.5277129135898445</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="R36" t="n">
+        <v>900000.0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T36" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1458.0</v>
+      </c>
+      <c r="V36" t="n">
+        <v>350000.0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B37" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F37" t="n">
+        <v>22.509526319248074</v>
+      </c>
+      <c r="G37" t="n">
+        <v>13.47355744429583</v>
+      </c>
+      <c r="H37" t="n">
+        <v>10.450132338391509</v>
+      </c>
+      <c r="I37" t="n">
+        <v>195.2853073653158</v>
+      </c>
+      <c r="J37" t="n">
+        <v>149.39469180480896</v>
+      </c>
+      <c r="K37" t="n">
+        <v>107.2985651424909</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.948829492436856</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0.961584853466815</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0.7356194624468793</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0.5283381347616252</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="R37" t="n">
+        <v>900000.0</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T37" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1458.0</v>
+      </c>
+      <c r="V37" t="n">
+        <v>380000.0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B38" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F38" t="n">
+        <v>22.27385678739238</v>
+      </c>
+      <c r="G38" t="n">
+        <v>13.391139218163852</v>
+      </c>
+      <c r="H38" t="n">
+        <v>10.444311063994288</v>
+      </c>
+      <c r="I38" t="n">
+        <v>195.2853073653158</v>
+      </c>
+      <c r="J38" t="n">
+        <v>149.40629839036086</v>
+      </c>
+      <c r="K38" t="n">
+        <v>107.36618574033818</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0.948829492436856</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0.961584853466815</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0.7356766132741368</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0.5286710985854253</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>900000.0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T38" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1458.0</v>
+      </c>
+      <c r="V38" t="n">
+        <v>400000.0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B39" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F39" t="n">
+        <v>22.530118328398125</v>
+      </c>
+      <c r="G39" t="n">
+        <v>13.505262534153484</v>
+      </c>
+      <c r="H39" t="n">
+        <v>10.450640981722316</v>
+      </c>
+      <c r="I39" t="n">
+        <v>195.2853073653158</v>
+      </c>
+      <c r="J39" t="n">
+        <v>149.38845187363853</v>
+      </c>
+      <c r="K39" t="n">
+        <v>107.25624039487509</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0.948829492436856</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0.961584853466815</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0.735588737025796</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0.528129727704365</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="R39" t="n">
+        <v>900000.0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T39" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1458.0</v>
+      </c>
+      <c r="V39" t="n">
+        <v>370000.0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B40" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F40" t="n">
+        <v>22.55071033754818</v>
+      </c>
+      <c r="G40" t="n">
+        <v>13.538630131411683</v>
+      </c>
+      <c r="H40" t="n">
+        <v>10.451149625053121</v>
+      </c>
+      <c r="I40" t="n">
+        <v>195.2853073653158</v>
+      </c>
+      <c r="J40" t="n">
+        <v>149.38221194246807</v>
+      </c>
+      <c r="K40" t="n">
+        <v>107.21391564725928</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0.948829492436856</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0.961584853466815</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0.7355580116047128</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0.5279213206471047</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="R40" t="n">
+        <v>900000.0</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T40" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1458.0</v>
+      </c>
+      <c r="V40" t="n">
+        <v>360000.0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B41" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F41" t="n">
+        <v>22.232672769092275</v>
+      </c>
+      <c r="G41" t="n">
+        <v>13.338443199937196</v>
+      </c>
+      <c r="H41" t="n">
+        <v>10.443293777332675</v>
+      </c>
+      <c r="I41" t="n">
+        <v>195.2853073653158</v>
+      </c>
+      <c r="J41" t="n">
+        <v>149.41443725294624</v>
+      </c>
+      <c r="K41" t="n">
+        <v>107.36618574033818</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.948829492436856</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0.961584853466815</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0.7357166890335073</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0.5286710985854253</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="R41" t="n">
+        <v>900000.0</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T41" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1458.0</v>
+      </c>
+      <c r="V41" t="n">
+        <v>420000.0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B42" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F42" t="n">
+        <v>22.48893431009802</v>
+      </c>
+      <c r="G42" t="n">
+        <v>13.443386976654065</v>
+      </c>
+      <c r="H42" t="n">
+        <v>10.449623695060703</v>
+      </c>
+      <c r="I42" t="n">
+        <v>195.2853073653158</v>
+      </c>
+      <c r="J42" t="n">
+        <v>149.40093173597936</v>
+      </c>
+      <c r="K42" t="n">
+        <v>107.34088989010671</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0.948829492436856</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0.961584853466815</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0.7356501878679624</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0.5285465418188854</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="R42" t="n">
+        <v>900000.0</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T42" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1458.0</v>
+      </c>
+      <c r="V42" t="n">
+        <v>390000.0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B43" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F43" t="n">
+        <v>22.253264778242325</v>
+      </c>
+      <c r="G43" t="n">
+        <v>13.364191988258682</v>
+      </c>
+      <c r="H43" t="n">
+        <v>10.443802420663483</v>
+      </c>
+      <c r="I43" t="n">
+        <v>195.2853073653158</v>
+      </c>
+      <c r="J43" t="n">
+        <v>149.41036782165355</v>
+      </c>
+      <c r="K43" t="n">
+        <v>107.36618574033818</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0.948829492436856</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0.961584853466815</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0.735696651153822</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0.5286710985854253</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="R43" t="n">
+        <v>900000.0</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T43" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1458.0</v>
+      </c>
+      <c r="V43" t="n">
+        <v>410000.0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B44" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F44" t="n">
+        <v>22.191488750792168</v>
+      </c>
+      <c r="G44" t="n">
+        <v>13.290214100340622</v>
+      </c>
+      <c r="H44" t="n">
+        <v>10.442276490671064</v>
+      </c>
+      <c r="I44" t="n">
+        <v>195.2853073653158</v>
+      </c>
+      <c r="J44" t="n">
+        <v>149.42257611553163</v>
+      </c>
+      <c r="K44" t="n">
+        <v>107.36618574033818</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0.948829492436856</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0.961584853466815</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0.7357567647928778</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0.5286710985854253</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="R44" t="n">
+        <v>900000.0</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T44" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1458.0</v>
+      </c>
+      <c r="V44" t="n">
+        <v>440000.0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B45" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F45" t="n">
+        <v>22.15509385235674</v>
+      </c>
+      <c r="G45" t="n">
+        <v>13.268212626005546</v>
+      </c>
+      <c r="H45" t="n">
+        <v>10.441817603593844</v>
+      </c>
+      <c r="I45" t="n">
+        <v>195.2853073653158</v>
+      </c>
+      <c r="J45" t="n">
+        <v>149.4285921885911</v>
+      </c>
+      <c r="K45" t="n">
+        <v>107.36618574033818</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0.948829492436856</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0.961584853466815</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0.7357863879366225</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0.5286710985854253</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="R45" t="n">
+        <v>900000.0</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T45" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1458.0</v>
+      </c>
+      <c r="V45" t="n">
+        <v>450000.0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B46" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F46" t="n">
+        <v>22.21208075994222</v>
+      </c>
+      <c r="G46" t="n">
+        <v>13.313809240995875</v>
+      </c>
+      <c r="H46" t="n">
+        <v>10.442785134001872</v>
+      </c>
+      <c r="I46" t="n">
+        <v>195.2853073653158</v>
+      </c>
+      <c r="J46" t="n">
+        <v>149.41850668423893</v>
+      </c>
+      <c r="K46" t="n">
+        <v>107.36618574033818</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0.948829492436856</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0.961584853466815</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0.7357367269131926</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0.5286710985854253</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="R46" t="n">
+        <v>900000.0</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T46" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1458.0</v>
+      </c>
+      <c r="V46" t="n">
+        <v>430000.0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B47" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C47" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F47" t="n">
+        <v>22.13463217237852</v>
+      </c>
+      <c r="G47" t="n">
+        <v>13.24645486355611</v>
+      </c>
+      <c r="H47" t="n">
+        <v>10.410864683711724</v>
+      </c>
+      <c r="I47" t="n">
+        <v>195.2853073653158</v>
+      </c>
+      <c r="J47" t="n">
+        <v>149.43266161988382</v>
+      </c>
+      <c r="K47" t="n">
+        <v>107.36618574033818</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0.948829492436856</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0.961584853466815</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0.7358064258163078</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0.5286710985854253</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="R47" t="n">
+        <v>900000.0</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T47" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1458.0</v>
+      </c>
+      <c r="V47" t="n">
+        <v>460000.0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B48" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C48" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F48" t="n">
+        <v>22.114170492400298</v>
+      </c>
+      <c r="G48" t="n">
+        <v>13.225547664991518</v>
+      </c>
+      <c r="H48" t="n">
+        <v>10.209776328380931</v>
+      </c>
+      <c r="I48" t="n">
+        <v>195.2853073653158</v>
+      </c>
+      <c r="J48" t="n">
+        <v>149.43673105117648</v>
+      </c>
+      <c r="K48" t="n">
+        <v>107.36618574033818</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0.948829492436856</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0.961584853466815</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0.735826463695993</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0.5286710985854253</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="R48" t="n">
+        <v>900000.0</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T48" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1458.0</v>
+      </c>
+      <c r="V48" t="n">
+        <v>470000.0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B49" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F49" t="n">
+        <v>22.093708812422083</v>
+      </c>
+      <c r="G49" t="n">
+        <v>13.205437870068973</v>
+      </c>
+      <c r="H49" t="n">
+        <v>10.017066654522255</v>
+      </c>
+      <c r="I49" t="n">
+        <v>195.2853073653158</v>
+      </c>
+      <c r="J49" t="n">
+        <v>149.44080048246917</v>
+      </c>
+      <c r="K49" t="n">
+        <v>107.36618574033818</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0.948829492436856</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0.961584853466815</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0.7358465015756783</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0.5286710985854253</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="R49" t="n">
+        <v>900000.0</v>
+      </c>
+      <c r="S49" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T49" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1458.0</v>
+      </c>
+      <c r="V49" t="n">
+        <v>480000.0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B50" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C50" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F50" t="n">
+        <v>22.073247132443868</v>
+      </c>
+      <c r="G50" t="n">
+        <v>13.18607665815733</v>
+      </c>
+      <c r="H50" t="n">
+        <v>9.832222681637404</v>
+      </c>
+      <c r="I50" t="n">
+        <v>195.2853073653158</v>
+      </c>
+      <c r="J50" t="n">
+        <v>149.4448699137619</v>
+      </c>
+      <c r="K50" t="n">
+        <v>107.36618574033818</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0.948829492436856</v>
+      </c>
+      <c r="N50" t="n">
+        <v>0.961584853466815</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0.7358665394553635</v>
+      </c>
+      <c r="P50" t="n">
+        <v>0.5286710985854253</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="R50" t="n">
+        <v>900000.0</v>
+      </c>
+      <c r="S50" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T50" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1458.0</v>
+      </c>
+      <c r="V50" t="n">
+        <v>490000.0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B51" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C51" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F51" t="n">
+        <v>22.05278545246565</v>
+      </c>
+      <c r="G51" t="n">
+        <v>13.167419114275926</v>
+      </c>
+      <c r="H51" t="n">
+        <v>9.654772467667948</v>
+      </c>
+      <c r="I51" t="n">
+        <v>195.2853073653158</v>
+      </c>
+      <c r="J51" t="n">
+        <v>149.44893934505458</v>
+      </c>
+      <c r="K51" t="n">
+        <v>107.36618574033818</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0.948829492436856</v>
+      </c>
+      <c r="N51" t="n">
+        <v>0.961584853466815</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0.7358865773350487</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0.5286710985854253</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="R51" t="n">
+        <v>900000.0</v>
+      </c>
+      <c r="S51" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T51" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1458.0</v>
+      </c>
+      <c r="V51" t="n">
+        <v>500000.0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B52" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C52" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F52" t="n">
+        <v>22.03232377248743</v>
+      </c>
+      <c r="G52" t="n">
+        <v>13.149423846187696</v>
+      </c>
+      <c r="H52" t="n">
+        <v>9.48428108561886</v>
+      </c>
+      <c r="I52" t="n">
+        <v>195.2853073653158</v>
+      </c>
+      <c r="J52" t="n">
+        <v>149.45300877634727</v>
+      </c>
+      <c r="K52" t="n">
+        <v>107.36618574033818</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0.948829492436856</v>
+      </c>
+      <c r="N52" t="n">
+        <v>0.961584853466815</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0.735906615214734</v>
+      </c>
+      <c r="P52" t="n">
+        <v>0.5286710985854253</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="R52" t="n">
+        <v>900000.0</v>
+      </c>
+      <c r="S52" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T52" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1458.0</v>
+      </c>
+      <c r="V52" t="n">
+        <v>510000.0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B53" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F53" t="n">
+        <v>21.991400412530993</v>
+      </c>
+      <c r="G53" t="n">
+        <v>13.111589328837972</v>
+      </c>
+      <c r="H53" t="n">
+        <v>9.162599232696055</v>
+      </c>
+      <c r="I53" t="n">
+        <v>195.2853073653158</v>
+      </c>
+      <c r="J53" t="n">
+        <v>149.46114763893266</v>
+      </c>
+      <c r="K53" t="n">
+        <v>107.36618574033818</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0.948829492436856</v>
+      </c>
+      <c r="N53" t="n">
+        <v>0.961584853466815</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0.7359466909741044</v>
+      </c>
+      <c r="P53" t="n">
+        <v>0.5286710985854253</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="R53" t="n">
+        <v>900000.0</v>
+      </c>
+      <c r="S53" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T53" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1458.0</v>
+      </c>
+      <c r="V53" t="n">
+        <v>530000.0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B54" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C54" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F54" t="n">
+        <v>21.970938732552774</v>
+      </c>
+      <c r="G54" t="n">
+        <v>13.077688822371575</v>
+      </c>
+      <c r="H54" t="n">
+        <v>9.010693913260287</v>
+      </c>
+      <c r="I54" t="n">
+        <v>195.2853073653158</v>
+      </c>
+      <c r="J54" t="n">
+        <v>149.46521707022535</v>
+      </c>
+      <c r="K54" t="n">
+        <v>107.36618574033818</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0.948829492436856</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0.961584853466815</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0.7359667288537896</v>
+      </c>
+      <c r="P54" t="n">
+        <v>0.5286710985854253</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="R54" t="n">
+        <v>900000.0</v>
+      </c>
+      <c r="S54" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T54" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1458.0</v>
+      </c>
+      <c r="V54" t="n">
+        <v>540000.0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B55" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F55" t="n">
+        <v>22.01186209250921</v>
+      </c>
+      <c r="G55" t="n">
+        <v>13.132052645673797</v>
+      </c>
+      <c r="H55" t="n">
+        <v>9.320347064417817</v>
+      </c>
+      <c r="I55" t="n">
+        <v>195.2853073653158</v>
+      </c>
+      <c r="J55" t="n">
+        <v>149.45707820763997</v>
+      </c>
+      <c r="K55" t="n">
+        <v>107.36618574033818</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0.948829492436856</v>
+      </c>
+      <c r="N55" t="n">
+        <v>0.961584853466815</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0.7359266530944192</v>
+      </c>
+      <c r="P55" t="n">
+        <v>0.5286710985854253</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="R55" t="n">
+        <v>900000.0</v>
+      </c>
+      <c r="S55" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T55" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1458.0</v>
+      </c>
+      <c r="V55" t="n">
+        <v>520000.0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B56" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F56" t="n">
+        <v>21.909553692618122</v>
+      </c>
+      <c r="G56" t="n">
+        <v>12.983130839040037</v>
+      </c>
+      <c r="H56" t="n">
+        <v>8.586958022202616</v>
+      </c>
+      <c r="I56" t="n">
+        <v>195.2853073653158</v>
+      </c>
+      <c r="J56" t="n">
+        <v>149.47742536410345</v>
+      </c>
+      <c r="K56" t="n">
+        <v>107.36618574033818</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0.948829492436856</v>
+      </c>
+      <c r="N56" t="n">
+        <v>0.961584853466815</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0.7360268424928453</v>
+      </c>
+      <c r="P56" t="n">
+        <v>0.5286710985854253</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="R56" t="n">
+        <v>900000.0</v>
+      </c>
+      <c r="S56" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T56" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1458.0</v>
+      </c>
+      <c r="V56" t="n">
+        <v>570000.0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B57" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C57" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F57" t="n">
+        <v>21.950477052574556</v>
+      </c>
+      <c r="G57" t="n">
+        <v>13.045025001995763</v>
+      </c>
+      <c r="H57" t="n">
+        <v>8.864312423622183</v>
+      </c>
+      <c r="I57" t="n">
+        <v>195.2853073653158</v>
+      </c>
+      <c r="J57" t="n">
+        <v>149.46928650151804</v>
+      </c>
+      <c r="K57" t="n">
+        <v>107.36618574033818</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0.948829492436856</v>
+      </c>
+      <c r="N57" t="n">
+        <v>0.961584853466815</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0.7359867667334749</v>
+      </c>
+      <c r="P57" t="n">
+        <v>0.5286710985854253</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="R57" t="n">
+        <v>900000.0</v>
+      </c>
+      <c r="S57" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T57" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1458.0</v>
+      </c>
+      <c r="V57" t="n">
+        <v>550000.0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B58" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F58" t="n">
+        <v>21.889092012639907</v>
+      </c>
+      <c r="G58" t="n">
+        <v>12.95377481511165</v>
+      </c>
+      <c r="H58" t="n">
+        <v>8.455453780150235</v>
+      </c>
+      <c r="I58" t="n">
+        <v>195.2853073653158</v>
+      </c>
+      <c r="J58" t="n">
+        <v>149.48149479539612</v>
+      </c>
+      <c r="K58" t="n">
+        <v>107.36618574033818</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0.948829492436856</v>
+      </c>
+      <c r="N58" t="n">
+        <v>0.961584853466815</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0.7360468803725305</v>
+      </c>
+      <c r="P58" t="n">
+        <v>0.5286710985854253</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="R58" t="n">
+        <v>900000.0</v>
+      </c>
+      <c r="S58" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T58" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1458.0</v>
+      </c>
+      <c r="V58" t="n">
+        <v>580000.0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B59" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C59" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D59" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F59" t="n">
+        <v>21.93001537259634</v>
+      </c>
+      <c r="G59" t="n">
+        <v>13.013527414128502</v>
+      </c>
+      <c r="H59" t="n">
+        <v>8.723158844328296</v>
+      </c>
+      <c r="I59" t="n">
+        <v>195.2853073653158</v>
+      </c>
+      <c r="J59" t="n">
+        <v>149.47335593281073</v>
+      </c>
+      <c r="K59" t="n">
+        <v>107.36618574033818</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0.948829492436856</v>
+      </c>
+      <c r="N59" t="n">
+        <v>0.961584853466815</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0.73600680461316</v>
+      </c>
+      <c r="P59" t="n">
+        <v>0.5286710985854253</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="R59" t="n">
+        <v>900000.0</v>
+      </c>
+      <c r="S59" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T59" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1458.0</v>
+      </c>
+      <c r="V59" t="n">
+        <v>560000.0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B60" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C60" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D60" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F60" t="n">
+        <v>21.868630332661688</v>
+      </c>
+      <c r="G60" t="n">
+        <v>12.925403213928947</v>
+      </c>
+      <c r="H60" t="n">
+        <v>8.328407309014883</v>
+      </c>
+      <c r="I60" t="n">
+        <v>195.2853073653158</v>
+      </c>
+      <c r="J60" t="n">
+        <v>149.4855642266888</v>
+      </c>
+      <c r="K60" t="n">
+        <v>107.36618574033818</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0.948829492436856</v>
+      </c>
+      <c r="N60" t="n">
+        <v>0.961584853466815</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0.7360669182522157</v>
+      </c>
+      <c r="P60" t="n">
+        <v>0.5286710985854253</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="R60" t="n">
+        <v>900000.0</v>
+      </c>
+      <c r="S60" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T60" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1458.0</v>
+      </c>
+      <c r="V60" t="n">
+        <v>590000.0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B61" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C61" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D61" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F61" t="n">
+        <v>21.848168652683473</v>
+      </c>
+      <c r="G61" t="n">
+        <v>12.897963859997342</v>
+      </c>
+      <c r="H61" t="n">
+        <v>8.205595720250711</v>
+      </c>
+      <c r="I61" t="n">
+        <v>195.2853073653158</v>
+      </c>
+      <c r="J61" t="n">
+        <v>149.48963365798153</v>
+      </c>
+      <c r="K61" t="n">
+        <v>107.36618574033818</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0.948829492436856</v>
+      </c>
+      <c r="N61" t="n">
+        <v>0.961584853466815</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0.736086956131901</v>
+      </c>
+      <c r="P61" t="n">
+        <v>0.5286710985854253</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="R61" t="n">
+        <v>900000.0</v>
+      </c>
+      <c r="S61" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T61" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1458.0</v>
+      </c>
+      <c r="V61" t="n">
+        <v>600000.0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B62" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C62" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D62" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F62" t="n">
+        <v>21.807245292727032</v>
+      </c>
+      <c r="G62" t="n">
+        <v>12.84569094498975</v>
+      </c>
+      <c r="H62" t="n">
+        <v>7.971857535183414</v>
+      </c>
+      <c r="I62" t="n">
+        <v>195.2853073653158</v>
+      </c>
+      <c r="J62" t="n">
+        <v>149.49777252056688</v>
+      </c>
+      <c r="K62" t="n">
+        <v>107.36618574033818</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0.948829492436856</v>
+      </c>
+      <c r="N62" t="n">
+        <v>0.961584853466815</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0.7361270318912714</v>
+      </c>
+      <c r="P62" t="n">
+        <v>0.5286710985854253</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="R62" t="n">
+        <v>900000.0</v>
+      </c>
+      <c r="S62" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T62" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1458.0</v>
+      </c>
+      <c r="V62" t="n">
+        <v>620000.0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B63" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C63" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D63" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F63" t="n">
+        <v>21.745860252792383</v>
+      </c>
+      <c r="G63" t="n">
+        <v>12.773161160275635</v>
+      </c>
+      <c r="H63" t="n">
+        <v>7.6482200481671585</v>
+      </c>
+      <c r="I63" t="n">
+        <v>195.2853073653158</v>
+      </c>
+      <c r="J63" t="n">
+        <v>149.509980814445</v>
+      </c>
+      <c r="K63" t="n">
+        <v>107.36618574033818</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0.948829492436856</v>
+      </c>
+      <c r="N63" t="n">
+        <v>0.961584853466815</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0.736187145530327</v>
+      </c>
+      <c r="P63" t="n">
+        <v>0.5286710985854253</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="R63" t="n">
+        <v>900000.0</v>
+      </c>
+      <c r="S63" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T63" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1458.0</v>
+      </c>
+      <c r="V63" t="n">
+        <v>650000.0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B64" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C64" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D64" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F64" t="n">
+        <v>21.827706972705254</v>
+      </c>
+      <c r="G64" t="n">
+        <v>12.871408189718633</v>
+      </c>
+      <c r="H64" t="n">
+        <v>8.086810740954217</v>
+      </c>
+      <c r="I64" t="n">
+        <v>195.2853073653158</v>
+      </c>
+      <c r="J64" t="n">
+        <v>149.49370308927422</v>
+      </c>
+      <c r="K64" t="n">
+        <v>107.36618574033818</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0.948829492436856</v>
+      </c>
+      <c r="N64" t="n">
+        <v>0.961584853466815</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0.7361069940115862</v>
+      </c>
+      <c r="P64" t="n">
+        <v>0.5286710985854253</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="R64" t="n">
+        <v>900000.0</v>
+      </c>
+      <c r="S64" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T64" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1458.0</v>
+      </c>
+      <c r="V64" t="n">
+        <v>610000.0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B65" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C65" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D65" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F65" t="n">
+        <v>21.725398572814164</v>
+      </c>
+      <c r="G65" t="n">
+        <v>12.750402041621532</v>
+      </c>
+      <c r="H65" t="n">
+        <v>7.54687901687924</v>
+      </c>
+      <c r="I65" t="n">
+        <v>195.2853073653158</v>
+      </c>
+      <c r="J65" t="n">
+        <v>149.51405024573768</v>
+      </c>
+      <c r="K65" t="n">
+        <v>107.36618574033818</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0.948829492436856</v>
+      </c>
+      <c r="N65" t="n">
+        <v>0.961584853466815</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0.7362071834100123</v>
+      </c>
+      <c r="P65" t="n">
+        <v>0.5286710985854253</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="R65" t="n">
+        <v>900000.0</v>
+      </c>
+      <c r="S65" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T65" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1458.0</v>
+      </c>
+      <c r="V65" t="n">
+        <v>660000.0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B66" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C66" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D66" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F66" t="n">
+        <v>21.766321932770598</v>
+      </c>
+      <c r="G66" t="n">
+        <v>12.796605599525206</v>
+      </c>
+      <c r="H66" t="n">
+        <v>7.752727986682826</v>
+      </c>
+      <c r="I66" t="n">
+        <v>195.2853073653158</v>
+      </c>
+      <c r="J66" t="n">
+        <v>149.5059113831523</v>
+      </c>
+      <c r="K66" t="n">
+        <v>107.36618574033818</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0.948829492436856</v>
+      </c>
+      <c r="N66" t="n">
+        <v>0.961584853466815</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0.7361671076506419</v>
+      </c>
+      <c r="P66" t="n">
+        <v>0.5286710985854253</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="R66" t="n">
+        <v>900000.0</v>
+      </c>
+      <c r="S66" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T66" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1458.0</v>
+      </c>
+      <c r="V66" t="n">
+        <v>640000.0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B67" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C67" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D67" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F67" t="n">
+        <v>21.786783612748817</v>
+      </c>
+      <c r="G67" t="n">
+        <v>12.820769897399671</v>
+      </c>
+      <c r="H67" t="n">
+        <v>7.8605536375323215</v>
+      </c>
+      <c r="I67" t="n">
+        <v>195.2853073653158</v>
+      </c>
+      <c r="J67" t="n">
+        <v>149.50184195185957</v>
+      </c>
+      <c r="K67" t="n">
+        <v>107.36618574033818</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0.948829492436856</v>
+      </c>
+      <c r="N67" t="n">
+        <v>0.961584853466815</v>
+      </c>
+      <c r="O67" t="n">
+        <v>0.7361470697709566</v>
+      </c>
+      <c r="P67" t="n">
+        <v>0.5286710985854253</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="R67" t="n">
+        <v>900000.0</v>
+      </c>
+      <c r="S67" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T67" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1458.0</v>
+      </c>
+      <c r="V67" t="n">
+        <v>630000.0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B68" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C68" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D68" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F68" t="n">
+        <v>21.704936892835946</v>
+      </c>
+      <c r="G68" t="n">
+        <v>12.728295874374671</v>
+      </c>
+      <c r="H68" t="n">
+        <v>7.4485630910029</v>
+      </c>
+      <c r="I68" t="n">
+        <v>195.2853073653158</v>
+      </c>
+      <c r="J68" t="n">
+        <v>149.51811967703037</v>
+      </c>
+      <c r="K68" t="n">
+        <v>107.36618574033818</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0.948829492436856</v>
+      </c>
+      <c r="N68" t="n">
+        <v>0.961584853466815</v>
+      </c>
+      <c r="O68" t="n">
+        <v>0.7362272212896975</v>
+      </c>
+      <c r="P68" t="n">
+        <v>0.5286710985854253</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="R68" t="n">
+        <v>900000.0</v>
+      </c>
+      <c r="S68" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T68" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1458.0</v>
+      </c>
+      <c r="V68" t="n">
+        <v>670000.0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B69" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C69" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D69" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F69" t="n">
+        <v>21.66401353287951</v>
+      </c>
+      <c r="G69" t="n">
+        <v>12.685922773463231</v>
+      </c>
+      <c r="H69" t="n">
+        <v>7.260480450195993</v>
+      </c>
+      <c r="I69" t="n">
+        <v>195.2853073653158</v>
+      </c>
+      <c r="J69" t="n">
+        <v>149.52625853961575</v>
+      </c>
+      <c r="K69" t="n">
+        <v>107.36618574033818</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0.948829492436856</v>
+      </c>
+      <c r="N69" t="n">
+        <v>0.961584853466815</v>
+      </c>
+      <c r="O69" t="n">
+        <v>0.736267297049068</v>
+      </c>
+      <c r="P69" t="n">
+        <v>0.5286710985854253</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="R69" t="n">
+        <v>900000.0</v>
+      </c>
+      <c r="S69" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T69" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1458.0</v>
+      </c>
+      <c r="V69" t="n">
+        <v>690000.0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B70" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C70" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D70" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F70" t="n">
+        <v>21.684475212857727</v>
+      </c>
+      <c r="G70" t="n">
+        <v>12.706812290971932</v>
+      </c>
+      <c r="H70" t="n">
+        <v>7.3531388100052775</v>
+      </c>
+      <c r="I70" t="n">
+        <v>195.2853073653158</v>
+      </c>
+      <c r="J70" t="n">
+        <v>149.52218910832306</v>
+      </c>
+      <c r="K70" t="n">
+        <v>107.36618574033818</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M70" t="n">
+        <v>0.948829492436856</v>
+      </c>
+      <c r="N70" t="n">
+        <v>0.961584853466815</v>
+      </c>
+      <c r="O70" t="n">
+        <v>0.7362472591693827</v>
+      </c>
+      <c r="P70" t="n">
+        <v>0.5286710985854253</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="R70" t="n">
+        <v>900000.0</v>
+      </c>
+      <c r="S70" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T70" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="U70" t="n">
+        <v>1458.0</v>
+      </c>
+      <c r="V70" t="n">
+        <v>680000.0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B71" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C71" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D71" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F71" t="n">
+        <v>21.59053567635224</v>
+      </c>
+      <c r="G71" t="n">
+        <v>12.622861441760934</v>
+      </c>
+      <c r="H71" t="n">
+        <v>6.997948430736348</v>
+      </c>
+      <c r="I71" t="n">
+        <v>195.2853073653158</v>
+      </c>
+      <c r="J71" t="n">
+        <v>149.5404134752606</v>
+      </c>
+      <c r="K71" t="n">
+        <v>107.36618574033818</v>
+      </c>
+      <c r="L71" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0.948829492436856</v>
+      </c>
+      <c r="N71" t="n">
+        <v>0.961584853466815</v>
+      </c>
+      <c r="O71" t="n">
+        <v>0.7363369959521833</v>
+      </c>
+      <c r="P71" t="n">
+        <v>0.5286710985854253</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="R71" t="n">
+        <v>900000.0</v>
+      </c>
+      <c r="S71" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T71" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="U71" t="n">
+        <v>1458.0</v>
+      </c>
+      <c r="V71" t="n">
+        <v>720000.0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B72" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C72" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D72" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F72" t="n">
+        <v>21.631201656686304</v>
+      </c>
+      <c r="G72" t="n">
+        <v>12.661919064205614</v>
+      </c>
+      <c r="H72" t="n">
+        <v>7.170469472095542</v>
+      </c>
+      <c r="I72" t="n">
+        <v>195.2853073653158</v>
+      </c>
+      <c r="J72" t="n">
+        <v>149.53227461267522</v>
+      </c>
+      <c r="K72" t="n">
+        <v>107.36618574033818</v>
+      </c>
+      <c r="L72" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M72" t="n">
+        <v>0.948829492436856</v>
+      </c>
+      <c r="N72" t="n">
+        <v>0.961584853466815</v>
+      </c>
+      <c r="O72" t="n">
+        <v>0.7362969201928129</v>
+      </c>
+      <c r="P72" t="n">
+        <v>0.5286710985854253</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="R72" t="n">
+        <v>900000.0</v>
+      </c>
+      <c r="S72" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T72" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="U72" t="n">
+        <v>1458.0</v>
+      </c>
+      <c r="V72" t="n">
+        <v>700000.0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B73" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C73" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D73" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F73" t="n">
+        <v>21.610868666519274</v>
+      </c>
+      <c r="G73" t="n">
+        <v>12.642130786338635</v>
+      </c>
+      <c r="H73" t="n">
+        <v>7.082994014504965</v>
+      </c>
+      <c r="I73" t="n">
+        <v>195.2853073653158</v>
+      </c>
+      <c r="J73" t="n">
+        <v>149.53634404396792</v>
+      </c>
+      <c r="K73" t="n">
+        <v>107.36618574033818</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M73" t="n">
+        <v>0.948829492436856</v>
+      </c>
+      <c r="N73" t="n">
+        <v>0.961584853466815</v>
+      </c>
+      <c r="O73" t="n">
+        <v>0.7363169580724981</v>
+      </c>
+      <c r="P73" t="n">
+        <v>0.5286710985854253</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="R73" t="n">
+        <v>900000.0</v>
+      </c>
+      <c r="S73" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T73" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="U73" t="n">
+        <v>1458.0</v>
+      </c>
+      <c r="V73" t="n">
+        <v>710000.0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B74" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C74" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D74" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F74" t="n">
+        <v>21.570202686185205</v>
+      </c>
+      <c r="G74" t="n">
+        <v>12.60408860966954</v>
+      </c>
+      <c r="H74" t="n">
+        <v>6.915232862961391</v>
+      </c>
+      <c r="I74" t="n">
+        <v>195.2853073653158</v>
+      </c>
+      <c r="J74" t="n">
+        <v>149.54448290655333</v>
+      </c>
+      <c r="K74" t="n">
+        <v>107.36618574033818</v>
+      </c>
+      <c r="L74" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M74" t="n">
+        <v>0.948829492436856</v>
+      </c>
+      <c r="N74" t="n">
+        <v>0.961584853466815</v>
+      </c>
+      <c r="O74" t="n">
+        <v>0.7363570338318686</v>
+      </c>
+      <c r="P74" t="n">
+        <v>0.5286710985854253</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="R74" t="n">
+        <v>900000.0</v>
+      </c>
+      <c r="S74" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T74" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="U74" t="n">
+        <v>1458.0</v>
+      </c>
+      <c r="V74" t="n">
+        <v>730000.0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B75" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C75" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D75" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F75" t="n">
+        <v>21.54986969601817</v>
+      </c>
+      <c r="G75" t="n">
+        <v>12.585791139574269</v>
+      </c>
+      <c r="H75" t="n">
+        <v>6.8347528510722455</v>
+      </c>
+      <c r="I75" t="n">
+        <v>195.2853073653158</v>
+      </c>
+      <c r="J75" t="n">
+        <v>149.548552337846</v>
+      </c>
+      <c r="K75" t="n">
+        <v>107.36618574033818</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.948829492436856</v>
+      </c>
+      <c r="N75" t="n">
+        <v>0.961584853466815</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0.7363770717115538</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0.5286710985854253</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>900000.0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T75" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1458.0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>740000.0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B76" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C76" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D76" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F76" t="n">
+        <v>21.48887072551707</v>
+      </c>
+      <c r="G76" t="n">
+        <v>12.533556642305777</v>
+      </c>
+      <c r="H76" t="n">
+        <v>6.605855154919998</v>
+      </c>
+      <c r="I76" t="n">
+        <v>195.2853073653158</v>
+      </c>
+      <c r="J76" t="n">
+        <v>149.5607606317241</v>
+      </c>
+      <c r="K76" t="n">
+        <v>107.36618574033818</v>
+      </c>
+      <c r="L76" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M76" t="n">
+        <v>0.9722796509951815</v>
+      </c>
+      <c r="N76" t="n">
+        <v>0.961584853466815</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0.7364371853506094</v>
+      </c>
+      <c r="P76" t="n">
+        <v>0.5286710985854253</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="R76" t="n">
+        <v>900000.0</v>
+      </c>
+      <c r="S76" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T76" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="U76" t="n">
+        <v>1458.0</v>
+      </c>
+      <c r="V76" t="n">
+        <v>770000.0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B77" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C77" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D77" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F77" t="n">
+        <v>21.52953670585114</v>
+      </c>
+      <c r="G77" t="n">
+        <v>12.567949062770216</v>
+      </c>
+      <c r="H77" t="n">
+        <v>6.756418972833474</v>
+      </c>
+      <c r="I77" t="n">
+        <v>195.2853073653158</v>
+      </c>
+      <c r="J77" t="n">
+        <v>149.55262176913868</v>
+      </c>
+      <c r="K77" t="n">
+        <v>107.36618574033818</v>
+      </c>
+      <c r="L77" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M77" t="n">
+        <v>0.948829492436856</v>
+      </c>
+      <c r="N77" t="n">
+        <v>0.961584853466815</v>
+      </c>
+      <c r="O77" t="n">
+        <v>0.7363971095912389</v>
+      </c>
+      <c r="P77" t="n">
+        <v>0.5286710985854253</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="R77" t="n">
+        <v>900000.0</v>
+      </c>
+      <c r="S77" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T77" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="U77" t="n">
+        <v>1458.0</v>
+      </c>
+      <c r="V77" t="n">
+        <v>750000.0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B78" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C78" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D78" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F78" t="n">
+        <v>21.509203715684105</v>
+      </c>
+      <c r="G78" t="n">
+        <v>12.550543511098509</v>
+      </c>
+      <c r="H78" t="n">
+        <v>6.680146512443095</v>
+      </c>
+      <c r="I78" t="n">
+        <v>195.2853073653158</v>
+      </c>
+      <c r="J78" t="n">
+        <v>149.5566912004314</v>
+      </c>
+      <c r="K78" t="n">
+        <v>107.36618574033818</v>
+      </c>
+      <c r="L78" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M78" t="n">
+        <v>0.9596526425406987</v>
+      </c>
+      <c r="N78" t="n">
+        <v>0.961584853466815</v>
+      </c>
+      <c r="O78" t="n">
+        <v>0.7364171474709241</v>
+      </c>
+      <c r="P78" t="n">
+        <v>0.5286710985854253</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="R78" t="n">
+        <v>900000.0</v>
+      </c>
+      <c r="S78" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T78" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="U78" t="n">
+        <v>1458.0</v>
+      </c>
+      <c r="V78" t="n">
+        <v>760000.0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B79" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C79" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D79" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F79" t="n">
+        <v>21.468537735350033</v>
+      </c>
+      <c r="G79" t="n">
+        <v>12.516971571386431</v>
+      </c>
+      <c r="H79" t="n">
+        <v>6.533468704000054</v>
+      </c>
+      <c r="I79" t="n">
+        <v>195.2853073653158</v>
+      </c>
+      <c r="J79" t="n">
+        <v>149.56483006301676</v>
+      </c>
+      <c r="K79" t="n">
+        <v>107.36618574033818</v>
+      </c>
+      <c r="L79" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M79" t="n">
+        <v>0.9849066594496645</v>
+      </c>
+      <c r="N79" t="n">
+        <v>0.961584853466815</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0.7364572232302946</v>
+      </c>
+      <c r="P79" t="n">
+        <v>0.5286710985854253</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="R79" t="n">
+        <v>900000.0</v>
+      </c>
+      <c r="S79" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T79" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="U79" t="n">
+        <v>1458.0</v>
+      </c>
+      <c r="V79" t="n">
+        <v>780000.0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B80" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C80" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D80" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F80" t="n">
+        <v>21.448204745183002</v>
+      </c>
+      <c r="G80" t="n">
+        <v>12.500772307356502</v>
+      </c>
+      <c r="H80" t="n">
+        <v>6.462914821457833</v>
+      </c>
+      <c r="I80" t="n">
+        <v>195.2853073653158</v>
+      </c>
+      <c r="J80" t="n">
+        <v>149.56889949430948</v>
+      </c>
+      <c r="K80" t="n">
+        <v>107.36618574033818</v>
+      </c>
+      <c r="L80" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M80" t="n">
+        <v>0.9975336679041472</v>
+      </c>
+      <c r="N80" t="n">
+        <v>0.961584853466815</v>
+      </c>
+      <c r="O80" t="n">
+        <v>0.7364772611099799</v>
+      </c>
+      <c r="P80" t="n">
+        <v>0.5286710985854253</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="R80" t="n">
+        <v>900000.0</v>
+      </c>
+      <c r="S80" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T80" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="U80" t="n">
+        <v>1458.0</v>
+      </c>
+      <c r="V80" t="n">
+        <v>790000.0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B81" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C81" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D81" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F81" t="n">
+        <v>21.879081912194312</v>
+      </c>
+      <c r="G81" t="n">
+        <v>13.25943772204072</v>
+      </c>
+      <c r="H81" t="n">
+        <v>6.388105540830993</v>
+      </c>
+      <c r="I81" t="n">
+        <v>196.24345767714476</v>
+      </c>
+      <c r="J81" t="n">
+        <v>150.71876393233083</v>
+      </c>
+      <c r="K81" t="n">
+        <v>107.36618574033818</v>
+      </c>
+      <c r="L81" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M81" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="N81" t="n">
+        <v>0.9663027856022608</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0.742139193602797</v>
+      </c>
+      <c r="P81" t="n">
+        <v>0.5286710985854253</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="R81" t="n">
+        <v>900000.0</v>
+      </c>
+      <c r="S81" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T81" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="U81" t="n">
+        <v>1458.0</v>
+      </c>
+      <c r="V81" t="n">
+        <v>800000.0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B82" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C82" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D82" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F82" t="n">
+        <v>21.868877644970524</v>
+      </c>
+      <c r="G82" t="n">
+        <v>13.232671339135683</v>
+      </c>
+      <c r="H82" t="n">
+        <v>6.3137003710221435</v>
+      </c>
+      <c r="I82" t="n">
+        <v>196.24345767714476</v>
+      </c>
+      <c r="J82" t="n">
+        <v>150.7228333636235</v>
+      </c>
+      <c r="K82" t="n">
+        <v>107.36618574033818</v>
+      </c>
+      <c r="L82" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M82" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="N82" t="n">
+        <v>0.9663027856022608</v>
+      </c>
+      <c r="O82" t="n">
+        <v>0.7421592314824823</v>
+      </c>
+      <c r="P82" t="n">
+        <v>0.5286710985854253</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="R82" t="n">
+        <v>900000.0</v>
+      </c>
+      <c r="S82" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T82" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="U82" t="n">
+        <v>1458.0</v>
+      </c>
+      <c r="V82" t="n">
+        <v>810000.0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B83" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C83" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D83" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F83" t="n">
+        <v>21.858673377746733</v>
+      </c>
+      <c r="G83" t="n">
+        <v>13.206561804212292</v>
+      </c>
+      <c r="H83" t="n">
+        <v>6.241109961452534</v>
+      </c>
+      <c r="I83" t="n">
+        <v>196.24345767714476</v>
+      </c>
+      <c r="J83" t="n">
+        <v>150.72690279491619</v>
+      </c>
+      <c r="K83" t="n">
+        <v>107.36618574033818</v>
+      </c>
+      <c r="L83" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M83" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="N83" t="n">
+        <v>0.9663027856022608</v>
+      </c>
+      <c r="O83" t="n">
+        <v>0.7421792693621675</v>
+      </c>
+      <c r="P83" t="n">
+        <v>0.5286710985854253</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="R83" t="n">
+        <v>900000.0</v>
+      </c>
+      <c r="S83" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T83" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="U83" t="n">
+        <v>1458.0</v>
+      </c>
+      <c r="V83" t="n">
+        <v>820000.0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B84" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C84" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D84" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E84" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F84" t="n">
+        <v>21.84846911052295</v>
+      </c>
+      <c r="G84" t="n">
+        <v>13.181084103949242</v>
+      </c>
+      <c r="H84" t="n">
+        <v>6.170268718378577</v>
+      </c>
+      <c r="I84" t="n">
+        <v>196.24345767714476</v>
+      </c>
+      <c r="J84" t="n">
+        <v>150.7309722262089</v>
+      </c>
+      <c r="K84" t="n">
+        <v>107.36618574033818</v>
+      </c>
+      <c r="L84" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M84" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="N84" t="n">
+        <v>0.9663027856022608</v>
+      </c>
+      <c r="O84" t="n">
+        <v>0.7421993072418527</v>
+      </c>
+      <c r="P84" t="n">
+        <v>0.5286710985854253</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="R84" t="n">
+        <v>900000.0</v>
+      </c>
+      <c r="S84" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T84" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="U84" t="n">
+        <v>1458.0</v>
+      </c>
+      <c r="V84" t="n">
+        <v>830000.0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B85" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C85" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D85" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F85" t="n">
+        <v>21.83826484329916</v>
+      </c>
+      <c r="G85" t="n">
+        <v>13.15621447597799</v>
+      </c>
+      <c r="H85" t="n">
+        <v>6.101114171568287</v>
+      </c>
+      <c r="I85" t="n">
+        <v>196.24345767714476</v>
+      </c>
+      <c r="J85" t="n">
+        <v>150.73504165750157</v>
+      </c>
+      <c r="K85" t="n">
+        <v>107.36618574033818</v>
+      </c>
+      <c r="L85" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M85" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="N85" t="n">
+        <v>0.9663027856022608</v>
+      </c>
+      <c r="O85" t="n">
+        <v>0.7422193451215379</v>
+      </c>
+      <c r="P85" t="n">
+        <v>0.5286710985854253</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="R85" t="n">
+        <v>900000.0</v>
+      </c>
+      <c r="S85" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T85" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="U85" t="n">
+        <v>1458.0</v>
+      </c>
+      <c r="V85" t="n">
+        <v>840000.0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B86" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C86" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D86" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F86" t="n">
+        <v>21.828060576075373</v>
+      </c>
+      <c r="G86" t="n">
+        <v>13.131930331818603</v>
+      </c>
+      <c r="H86" t="n">
+        <v>6.033586790565296</v>
+      </c>
+      <c r="I86" t="n">
+        <v>196.24345767714476</v>
+      </c>
+      <c r="J86" t="n">
+        <v>150.7391110887943</v>
+      </c>
+      <c r="K86" t="n">
+        <v>107.36618574033818</v>
+      </c>
+      <c r="L86" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M86" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="N86" t="n">
+        <v>0.9663027856022608</v>
+      </c>
+      <c r="O86" t="n">
+        <v>0.7422393830012232</v>
+      </c>
+      <c r="P86" t="n">
+        <v>0.5286710985854253</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="R86" t="n">
+        <v>900000.0</v>
+      </c>
+      <c r="S86" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T86" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="U86" t="n">
+        <v>1458.0</v>
+      </c>
+      <c r="V86" t="n">
+        <v>850000.0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B87" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C87" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D87" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E87" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F87" t="n">
+        <v>21.81785630885158</v>
+      </c>
+      <c r="G87" t="n">
+        <v>13.108210185432048</v>
+      </c>
+      <c r="H87" t="n">
+        <v>5.967629813771678</v>
+      </c>
+      <c r="I87" t="n">
+        <v>196.24345767714476</v>
+      </c>
+      <c r="J87" t="n">
+        <v>150.74318052008698</v>
+      </c>
+      <c r="K87" t="n">
+        <v>107.36618574033818</v>
+      </c>
+      <c r="L87" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M87" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="N87" t="n">
+        <v>0.9663027856022608</v>
+      </c>
+      <c r="O87" t="n">
+        <v>0.7422594208809083</v>
+      </c>
+      <c r="P87" t="n">
+        <v>0.5286710985854253</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="R87" t="n">
+        <v>900000.0</v>
+      </c>
+      <c r="S87" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T87" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="U87" t="n">
+        <v>1458.0</v>
+      </c>
+      <c r="V87" t="n">
+        <v>860000.0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B88" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C88" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D88" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E88" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F88" t="n">
+        <v>21.797447774404006</v>
+      </c>
+      <c r="G88" t="n">
+        <v>13.062381060931152</v>
+      </c>
+      <c r="H88" t="n">
+        <v>5.840212926784006</v>
+      </c>
+      <c r="I88" t="n">
+        <v>196.24345767714476</v>
+      </c>
+      <c r="J88" t="n">
+        <v>150.75131938267236</v>
+      </c>
+      <c r="K88" t="n">
+        <v>107.36618574033818</v>
+      </c>
+      <c r="L88" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M88" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="N88" t="n">
+        <v>0.9663027856022608</v>
+      </c>
+      <c r="O88" t="n">
+        <v>0.7422994966402788</v>
+      </c>
+      <c r="P88" t="n">
+        <v>0.5286710985854253</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="R88" t="n">
+        <v>900000.0</v>
+      </c>
+      <c r="S88" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T88" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="U88" t="n">
+        <v>1458.0</v>
+      </c>
+      <c r="V88" t="n">
+        <v>880000.0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B89" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C89" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D89" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E89" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F89" t="n">
+        <v>21.807652041627794</v>
+      </c>
+      <c r="G89" t="n">
+        <v>13.085033586917898</v>
+      </c>
+      <c r="H89" t="n">
+        <v>5.903189089318143</v>
+      </c>
+      <c r="I89" t="n">
+        <v>196.24345767714476</v>
+      </c>
+      <c r="J89" t="n">
+        <v>150.74724995137964</v>
+      </c>
+      <c r="K89" t="n">
+        <v>107.36618574033818</v>
+      </c>
+      <c r="L89" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M89" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="N89" t="n">
+        <v>0.9663027856022608</v>
+      </c>
+      <c r="O89" t="n">
+        <v>0.7422794587605936</v>
+      </c>
+      <c r="P89" t="n">
+        <v>0.5286710985854253</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="R89" t="n">
+        <v>900000.0</v>
+      </c>
+      <c r="S89" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T89" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="U89" t="n">
+        <v>1458.0</v>
+      </c>
+      <c r="V89" t="n">
+        <v>870000.0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B90" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C90" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D90" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E90" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F90" t="n">
+        <v>21.78724350718022</v>
+      </c>
+      <c r="G90" t="n">
+        <v>13.040234049431394</v>
+      </c>
+      <c r="H90" t="n">
+        <v>5.778651958913559</v>
+      </c>
+      <c r="I90" t="n">
+        <v>196.24345767714476</v>
+      </c>
+      <c r="J90" t="n">
+        <v>150.75538881396506</v>
+      </c>
+      <c r="K90" t="n">
+        <v>107.36618574033818</v>
+      </c>
+      <c r="L90" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M90" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="N90" t="n">
+        <v>0.9663027856022608</v>
+      </c>
+      <c r="O90" t="n">
+        <v>0.742319534519964</v>
+      </c>
+      <c r="P90" t="n">
+        <v>0.5286710985854253</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="R90" t="n">
+        <v>900000.0</v>
+      </c>
+      <c r="S90" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T90" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="U90" t="n">
+        <v>1458.0</v>
+      </c>
+      <c r="V90" t="n">
+        <v>890000.0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B91" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C91" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D91" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E91" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F91" t="n">
+        <v>21.77703923995643</v>
+      </c>
+      <c r="G91" t="n">
+        <v>13.018574858413603</v>
+      </c>
+      <c r="H91" t="n">
+        <v>5.718459012551343</v>
+      </c>
+      <c r="I91" t="n">
+        <v>196.24345767714476</v>
+      </c>
+      <c r="J91" t="n">
+        <v>150.75945824525772</v>
+      </c>
+      <c r="K91" t="n">
+        <v>107.36618574033818</v>
+      </c>
+      <c r="L91" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M91" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="N91" t="n">
+        <v>0.9663027856022608</v>
+      </c>
+      <c r="O91" t="n">
+        <v>0.7423395723996493</v>
+      </c>
+      <c r="P91" t="n">
+        <v>0.5286710985854253</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="R91" t="n">
+        <v>900000.0</v>
+      </c>
+      <c r="S91" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T91" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="U91" t="n">
+        <v>1458.0</v>
+      </c>
+      <c r="V91" t="n">
+        <v>900000.0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B92" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C92" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D92" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F92" t="n">
+        <v>21.766834972732642</v>
+      </c>
+      <c r="G92" t="n">
+        <v>12.997386608301664</v>
+      </c>
+      <c r="H92" t="n">
+        <v>5.659588988087197</v>
+      </c>
+      <c r="I92" t="n">
+        <v>196.24345767714476</v>
+      </c>
+      <c r="J92" t="n">
+        <v>150.76352767655044</v>
+      </c>
+      <c r="K92" t="n">
+        <v>107.36618574033818</v>
+      </c>
+      <c r="L92" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M92" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="N92" t="n">
+        <v>0.9663027856022608</v>
+      </c>
+      <c r="O92" t="n">
+        <v>0.7423596102793345</v>
+      </c>
+      <c r="P92" t="n">
+        <v>0.5286710985854253</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="R92" t="n">
+        <v>900000.0</v>
+      </c>
+      <c r="S92" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T92" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="U92" t="n">
+        <v>1458.0</v>
+      </c>
+      <c r="V92" t="n">
+        <v>910000.0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B93" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C93" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D93" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F93" t="n">
+        <v>21.746426438285063</v>
+      </c>
+      <c r="G93" t="n">
+        <v>12.956359210341631</v>
+      </c>
+      <c r="H93" t="n">
+        <v>5.545647005253369</v>
+      </c>
+      <c r="I93" t="n">
+        <v>196.24345767714476</v>
+      </c>
+      <c r="J93" t="n">
+        <v>150.77166653913582</v>
+      </c>
+      <c r="K93" t="n">
+        <v>107.36618574033818</v>
+      </c>
+      <c r="L93" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M93" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="N93" t="n">
+        <v>0.9663027856022608</v>
+      </c>
+      <c r="O93" t="n">
+        <v>0.7423996860387049</v>
+      </c>
+      <c r="P93" t="n">
+        <v>0.5286710985854253</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="R93" t="n">
+        <v>900000.0</v>
+      </c>
+      <c r="S93" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T93" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="U93" t="n">
+        <v>1458.0</v>
+      </c>
+      <c r="V93" t="n">
+        <v>930000.0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B94" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C94" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D94" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F94" t="n">
+        <v>21.75663070550885</v>
+      </c>
+      <c r="G94" t="n">
+        <v>12.976653187714632</v>
+      </c>
+      <c r="H94" t="n">
+        <v>5.601998746763577</v>
+      </c>
+      <c r="I94" t="n">
+        <v>196.24345767714476</v>
+      </c>
+      <c r="J94" t="n">
+        <v>150.76759710784316</v>
+      </c>
+      <c r="K94" t="n">
+        <v>107.36618574033818</v>
+      </c>
+      <c r="L94" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M94" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="N94" t="n">
+        <v>0.9663027856022608</v>
+      </c>
+      <c r="O94" t="n">
+        <v>0.7423796481590197</v>
+      </c>
+      <c r="P94" t="n">
+        <v>0.5286710985854253</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="R94" t="n">
+        <v>900000.0</v>
+      </c>
+      <c r="S94" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T94" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="U94" t="n">
+        <v>1458.0</v>
+      </c>
+      <c r="V94" t="n">
+        <v>920000.0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B95" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C95" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D95" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E95" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F95" t="n">
+        <v>21.726017903837487</v>
+      </c>
+      <c r="G95" t="n">
+        <v>12.91703142644935</v>
+      </c>
+      <c r="H95" t="n">
+        <v>5.43650257959149</v>
+      </c>
+      <c r="I95" t="n">
+        <v>196.24345767714476</v>
+      </c>
+      <c r="J95" t="n">
+        <v>150.77980540172123</v>
+      </c>
+      <c r="K95" t="n">
+        <v>107.36618574033818</v>
+      </c>
+      <c r="L95" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M95" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="N95" t="n">
+        <v>0.9663027856022608</v>
+      </c>
+      <c r="O95" t="n">
+        <v>0.7424397617980754</v>
+      </c>
+      <c r="P95" t="n">
+        <v>0.5286710985854253</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="R95" t="n">
+        <v>900000.0</v>
+      </c>
+      <c r="S95" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T95" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="U95" t="n">
+        <v>1458.0</v>
+      </c>
+      <c r="V95" t="n">
+        <v>950000.0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B96" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C96" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D96" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E96" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F96" t="n">
+        <v>21.73622217106128</v>
+      </c>
+      <c r="G96" t="n">
+        <v>12.93648997468463</v>
+      </c>
+      <c r="H96" t="n">
+        <v>5.490494236966781</v>
+      </c>
+      <c r="I96" t="n">
+        <v>196.24345767714476</v>
+      </c>
+      <c r="J96" t="n">
+        <v>150.7757359704285</v>
+      </c>
+      <c r="K96" t="n">
+        <v>107.36618574033818</v>
+      </c>
+      <c r="L96" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M96" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="N96" t="n">
+        <v>0.9663027856022608</v>
+      </c>
+      <c r="O96" t="n">
+        <v>0.7424197239183902</v>
+      </c>
+      <c r="P96" t="n">
+        <v>0.5286710985854253</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="R96" t="n">
+        <v>900000.0</v>
+      </c>
+      <c r="S96" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T96" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="U96" t="n">
+        <v>1458.0</v>
+      </c>
+      <c r="V96" t="n">
+        <v>940000.0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B97" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C97" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D97" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E97" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F97" t="n">
+        <v>21.7158136366137</v>
+      </c>
+      <c r="G97" t="n">
+        <v>12.897970123383638</v>
+      </c>
+      <c r="H97" t="n">
+        <v>5.383635748411518</v>
+      </c>
+      <c r="I97" t="n">
+        <v>196.24345767714476</v>
+      </c>
+      <c r="J97" t="n">
+        <v>150.7838748330139</v>
+      </c>
+      <c r="K97" t="n">
+        <v>107.36618574033818</v>
+      </c>
+      <c r="L97" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M97" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="N97" t="n">
+        <v>0.9663027856022608</v>
+      </c>
+      <c r="O97" t="n">
+        <v>0.7424597996777605</v>
+      </c>
+      <c r="P97" t="n">
+        <v>0.5286710985854253</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="R97" t="n">
+        <v>900000.0</v>
+      </c>
+      <c r="S97" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T97" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="U97" t="n">
+        <v>1458.0</v>
+      </c>
+      <c r="V97" t="n">
+        <v>960000.0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B98" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C98" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D98" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E98" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F98" t="n">
+        <v>21.69540510216612</v>
+      </c>
+      <c r="G98" t="n">
+        <v>12.860988348672489</v>
+      </c>
+      <c r="H98" t="n">
+        <v>5.281138830817693</v>
+      </c>
+      <c r="I98" t="n">
+        <v>196.24345767714476</v>
+      </c>
+      <c r="J98" t="n">
+        <v>150.7920136955993</v>
+      </c>
+      <c r="K98" t="n">
+        <v>107.36618574033818</v>
+      </c>
+      <c r="L98" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M98" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="N98" t="n">
+        <v>0.9663027856022608</v>
+      </c>
+      <c r="O98" t="n">
+        <v>0.742499875437131</v>
+      </c>
+      <c r="P98" t="n">
+        <v>0.5286710985854253</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="R98" t="n">
+        <v>900000.0</v>
+      </c>
+      <c r="S98" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T98" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="U98" t="n">
+        <v>1458.0</v>
+      </c>
+      <c r="V98" t="n">
+        <v>980000.0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B99" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C99" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D99" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E99" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F99" t="n">
+        <v>21.705609369389908</v>
+      </c>
+      <c r="G99" t="n">
+        <v>12.87929320237975</v>
+      </c>
+      <c r="H99" t="n">
+        <v>5.331858954987834</v>
+      </c>
+      <c r="I99" t="n">
+        <v>196.24345767714476</v>
+      </c>
+      <c r="J99" t="n">
+        <v>150.7879442643066</v>
+      </c>
+      <c r="K99" t="n">
+        <v>107.36618574033818</v>
+      </c>
+      <c r="L99" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M99" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="N99" t="n">
+        <v>0.9663027856022608</v>
+      </c>
+      <c r="O99" t="n">
+        <v>0.7424798375574458</v>
+      </c>
+      <c r="P99" t="n">
+        <v>0.5286710985854253</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="R99" t="n">
+        <v>900000.0</v>
+      </c>
+      <c r="S99" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T99" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="U99" t="n">
+        <v>1458.0</v>
+      </c>
+      <c r="V99" t="n">
+        <v>970000.0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B100" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C100" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D100" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F100" t="n">
+        <v>21.685200834942336</v>
+      </c>
+      <c r="G100" t="n">
+        <v>12.843043766979395</v>
+      </c>
+      <c r="H100" t="n">
+        <v>5.231443355620688</v>
+      </c>
+      <c r="I100" t="n">
+        <v>196.24345767714476</v>
+      </c>
+      <c r="J100" t="n">
+        <v>150.79608312689197</v>
+      </c>
+      <c r="K100" t="n">
+        <v>107.36618574033818</v>
+      </c>
+      <c r="L100" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M100" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="N100" t="n">
+        <v>0.9663027856022608</v>
+      </c>
+      <c r="O100" t="n">
+        <v>0.7425199133168163</v>
+      </c>
+      <c r="P100" t="n">
+        <v>0.5286710985854253</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="R100" t="n">
+        <v>900000.0</v>
+      </c>
+      <c r="S100" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T100" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="U100" t="n">
+        <v>1458.0</v>
+      </c>
+      <c r="V100" t="n">
+        <v>990000.0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B101" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C101" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D101" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F101" t="n">
+        <v>21.674996567718548</v>
+      </c>
+      <c r="G101" t="n">
+        <v>12.825448154441741</v>
+      </c>
+      <c r="H101" t="n">
+        <v>5.182741789927622</v>
+      </c>
+      <c r="I101" t="n">
+        <v>196.24345767714476</v>
+      </c>
+      <c r="J101" t="n">
+        <v>150.8001525581847</v>
+      </c>
+      <c r="K101" t="n">
+        <v>107.36618574033818</v>
+      </c>
+      <c r="L101" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M101" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="N101" t="n">
+        <v>0.9663027856022608</v>
+      </c>
+      <c r="O101" t="n">
+        <v>0.7425399511965015</v>
+      </c>
+      <c r="P101" t="n">
+        <v>0.5286710985854253</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="R101" t="n">
+        <v>900000.0</v>
+      </c>
+      <c r="S101" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="T101" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="U101" t="n">
+        <v>1458.0</v>
+      </c>
+      <c r="V101" t="n">
+        <v>1000000.0</v>
       </c>
     </row>
   </sheetData>
